--- a/MANUAL/Evaluasi_Kinerja_Perawat_MCDM_v2.xlsx
+++ b/MANUAL/Evaluasi_Kinerja_Perawat_MCDM_v2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -744,48 +744,6 @@
   </cellStyleXfs>
   <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -943,16 +901,58 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,75 +1219,75 @@
   <dimension ref="A2:D10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="3" width="45" style="15" customWidth="1"/>
-    <col min="4" max="4" width="20" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
     </row>
     <row r="3" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="5" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="55"/>
     </row>
     <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="12"/>
+      <c r="D7" s="55"/>
     </row>
     <row r="8" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="55"/>
     </row>
     <row r="9" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="55"/>
     </row>
     <row r="10" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="12"/>
+      <c r="D10" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1309,1121 +1309,1121 @@
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="9" width="11" style="15" customWidth="1"/>
-    <col min="10" max="10" width="14" style="15" customWidth="1"/>
-    <col min="11" max="12" width="12" style="15" customWidth="1"/>
-    <col min="13" max="13" width="14" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
     </row>
     <row r="2" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
     </row>
     <row r="5" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="20">
+    <row r="6" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="6">
         <v>8</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="6">
         <v>7</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="6">
         <v>9</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="6">
         <v>8</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="6">
         <v>9</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="6">
         <v>7</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="6">
         <v>8</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="7">
         <f t="shared" ref="K6:K15" si="0">SUM(D6:J6)</f>
         <v>56</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="8">
         <f t="shared" ref="L6:L15" si="1">AVERAGE(D6:J6)</f>
         <v>8</v>
       </c>
-      <c r="M6" s="23" t="str">
+      <c r="M6" s="9" t="str">
         <f t="shared" ref="M6:M15" si="2">J25</f>
         <v>K1</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24">
+    <row r="7" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="10">
         <v>2</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="10">
         <v>5</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="10">
         <v>6</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="10">
         <v>5</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="10">
         <v>6</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="10">
         <v>5</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="10">
         <v>6</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="10">
         <v>5</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="12">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="13">
         <f t="shared" si="1"/>
         <v>5.4285714285714288</v>
       </c>
-      <c r="M7" s="23" t="str">
+      <c r="M7" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K3</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="20">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="6">
         <v>9</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="6">
         <v>9</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="6">
         <v>8</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="6">
         <v>9</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="6">
         <v>9</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="6">
         <v>8</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="6">
         <v>9</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="7">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="8">
         <f t="shared" si="1"/>
         <v>8.7142857142857135</v>
       </c>
-      <c r="M8" s="23" t="str">
+      <c r="M8" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K1</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="10">
         <v>4</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="10">
         <v>6</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="10">
         <v>5</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="10">
         <v>6</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="10">
         <v>5</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="10">
         <v>6</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="10">
         <v>5</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="10">
         <v>6</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="12">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="13">
         <f t="shared" si="1"/>
         <v>5.5714285714285712</v>
       </c>
-      <c r="M9" s="23" t="str">
+      <c r="M9" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K2</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="20">
+    <row r="10" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="6">
         <v>7</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="6">
         <v>8</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="6">
         <v>7</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="6">
         <v>8</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="6">
         <v>7</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="6">
         <v>8</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="6">
         <v>7</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="7">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="8">
         <f t="shared" si="1"/>
         <v>7.4285714285714288</v>
       </c>
-      <c r="M10" s="23" t="str">
+      <c r="M10" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K2</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24">
+    <row r="11" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="10">
         <v>6</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="10">
         <v>4</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="10">
         <v>5</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="10">
         <v>4</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="10">
         <v>5</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="10">
         <v>4</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="10">
         <v>5</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="10">
         <v>4</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="12">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="13">
         <f t="shared" si="1"/>
         <v>4.4285714285714288</v>
       </c>
-      <c r="M11" s="23" t="str">
+      <c r="M11" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K3</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20">
+    <row r="12" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="6">
         <v>9</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="6">
         <v>8</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="6">
         <v>9</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="6">
         <v>9</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="6">
         <v>8</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="6">
         <v>9</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="6">
         <v>8</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="7">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="8">
         <f t="shared" si="1"/>
         <v>8.5714285714285712</v>
       </c>
-      <c r="M12" s="23" t="str">
+      <c r="M12" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K1</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="24">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="10">
         <v>8</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="10">
         <v>6</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="10">
         <v>6</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="10">
         <v>7</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="10">
         <v>6</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="10">
         <v>7</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="10">
         <v>6</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="10">
         <v>7</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="12">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="13">
         <f t="shared" si="1"/>
         <v>6.4285714285714288</v>
       </c>
-      <c r="M13" s="23" t="str">
+      <c r="M13" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K2</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20">
+    <row r="14" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="6">
         <v>8</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="6">
         <v>9</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="6">
         <v>8</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="6">
         <v>8</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="6">
         <v>9</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="6">
         <v>9</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="6">
         <v>8</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="7">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="8">
         <f t="shared" si="1"/>
         <v>8.4285714285714288</v>
       </c>
-      <c r="M14" s="23" t="str">
+      <c r="M14" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K1</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="24">
+    <row r="15" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="10">
         <v>10</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="10">
         <v>5</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="10">
         <v>4</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="10">
         <v>5</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="10">
         <v>4</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="10">
         <v>5</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="10">
         <v>4</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="10">
         <v>5</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="12">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="13">
         <f t="shared" si="1"/>
         <v>4.5714285714285712</v>
       </c>
-      <c r="M15" s="23" t="str">
+      <c r="M15" s="9" t="str">
         <f t="shared" si="2"/>
         <v>K3</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="2:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="19" t="s">
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+    <row r="19" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="15">
         <v>8.5</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="15">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="15">
         <v>8.5</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="15">
         <v>8.5</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="15">
         <v>8.6999999999999993</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="15">
         <v>8.3000000000000007</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="15">
         <v>8.3000000000000007</v>
       </c>
-      <c r="J19" s="28" t="s">
+      <c r="J19" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
+    <row r="20" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="17">
         <v>6.5</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="17">
         <v>6.5</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="17">
         <v>6.7</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="17">
         <v>6.7</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="17">
         <v>6.7</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="17">
         <v>6.5</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="17">
         <v>6.7</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="32" t="s">
+    <row r="21" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="19">
         <v>4.7</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="19">
         <v>5</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="19">
         <v>4.7</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="19">
         <v>5</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="19">
         <v>4.7</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="19">
         <v>5</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="19">
         <v>4.7</v>
       </c>
-      <c r="J21" s="32" t="s">
+      <c r="J21" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+    </row>
+    <row r="24" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I24" s="19" t="s">
+      <c r="I24" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="20">
+    <row r="25" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B25" s="6">
         <v>1</v>
       </c>
-      <c r="C25" s="18" t="str">
+      <c r="C25" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C6</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="20">
         <f>(D6-C19)^2+(D6-D19)^2+(D6-E19)^2+(D6-F19)^2+(D6-G19)^2+(D6-H19)^2+(D6-I19)^2</f>
         <v>1.5100000000000005</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="20">
         <f>(D6-C20)^2+(D6-D20)^2+(D6-E20)^2+(D6-F20)^2+(D6-G20)^2+(D6-H20)^2+(D6-I20)^2</f>
         <v>13.509999999999998</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="20">
         <f>(D6-C21)^2+(D6-D21)^2+(D6-E21)^2+(D6-F21)^2+(D6-G21)^2+(D6-H21)^2+(D6-I21)^2</f>
         <v>70.56</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="20">
         <f t="shared" ref="G25:G34" si="3">SQRT(D25)</f>
         <v>1.228820572744451</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="20">
         <f t="shared" ref="H25:H34" si="4">SQRT(E25)</f>
         <v>3.675595189897821</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="20">
         <f t="shared" ref="I25:I34" si="5">SQRT(F25)</f>
         <v>8.4</v>
       </c>
-      <c r="J25" s="35" t="str">
+      <c r="J25" s="21" t="str">
         <f t="shared" ref="J25:J34" si="6">IF(AND(G25&lt;=H25,G25&lt;=I25),"K1",IF(H25&lt;=I25,"K2","K3"))</f>
         <v>K1</v>
       </c>
-      <c r="K25" s="35" t="str">
+      <c r="K25" s="21" t="str">
         <f t="shared" ref="K25:K34" si="7">IF(J25="K1","TINGGI",IF(J25="K2","SEDANG","RENDAH"))</f>
         <v>TINGGI</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="24">
+    <row r="26" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B26" s="10">
         <v>2</v>
       </c>
-      <c r="C26" s="25" t="str">
+      <c r="C26" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C7</f>
         <v>Budi Santoso</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="22">
         <f>(D7-C19)^2+(D7-D19)^2+(D7-E19)^2+(D7-F19)^2+(D7-G19)^2+(D7-H19)^2+(D7-I19)^2</f>
         <v>83.11</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="22">
         <f>(D7-C20)^2+(D7-D20)^2+(D7-E20)^2+(D7-F20)^2+(D7-G20)^2+(D7-H20)^2+(D7-I20)^2</f>
         <v>18.310000000000002</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="22">
         <f>(D7-C21)^2+(D7-D21)^2+(D7-E21)^2+(D7-F21)^2+(D7-G21)^2+(D7-H21)^2+(D7-I21)^2</f>
         <v>0.3599999999999996</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="22">
         <f t="shared" si="3"/>
         <v>9.1164686145458749</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="22">
         <f t="shared" si="4"/>
         <v>4.2790185790669337</v>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="22">
         <f t="shared" si="5"/>
         <v>0.59999999999999964</v>
       </c>
-      <c r="J26" s="37" t="str">
+      <c r="J26" s="23" t="str">
         <f t="shared" si="6"/>
         <v>K3</v>
       </c>
-      <c r="K26" s="37" t="str">
+      <c r="K26" s="23" t="str">
         <f t="shared" si="7"/>
         <v>RENDAH</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="20">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
         <v>3</v>
       </c>
-      <c r="C27" s="18" t="str">
+      <c r="C27" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C8</f>
         <v>Citra Dewi</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="20">
         <f>(D8-C19)^2+(D8-D19)^2+(D8-E19)^2+(D8-F19)^2+(D8-G19)^2+(D8-H19)^2+(D8-I19)^2</f>
         <v>2.3099999999999974</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="20">
         <f>(D8-C20)^2+(D8-D20)^2+(D8-E20)^2+(D8-F20)^2+(D8-G20)^2+(D8-H20)^2+(D8-I20)^2</f>
         <v>39.909999999999997</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="20">
         <f>(D8-C21)^2+(D8-D21)^2+(D8-E21)^2+(D8-F21)^2+(D8-G21)^2+(D8-H21)^2+(D8-I21)^2</f>
         <v>121.95999999999998</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="20">
         <f t="shared" si="3"/>
         <v>1.5198684153570654</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="20">
         <f t="shared" si="4"/>
         <v>6.3174361888348347</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="20">
         <f t="shared" si="5"/>
         <v>11.043550153822817</v>
       </c>
-      <c r="J27" s="35" t="str">
+      <c r="J27" s="21" t="str">
         <f t="shared" si="6"/>
         <v>K1</v>
       </c>
-      <c r="K27" s="35" t="str">
+      <c r="K27" s="21" t="str">
         <f t="shared" si="7"/>
         <v>TINGGI</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="24">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="10">
         <v>4</v>
       </c>
-      <c r="C28" s="25" t="str">
+      <c r="C28" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C9</f>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="22">
         <f>(D9-C19)^2+(D9-D19)^2+(D9-E19)^2+(D9-F19)^2+(D9-G19)^2+(D9-H19)^2+(D9-I19)^2</f>
         <v>41.910000000000011</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="22">
         <f>(D9-C20)^2+(D9-D20)^2+(D9-E20)^2+(D9-F20)^2+(D9-G20)^2+(D9-H20)^2+(D9-I20)^2</f>
         <v>2.7100000000000009</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="22">
         <f>(D9-C21)^2+(D9-D21)^2+(D9-E21)^2+(D9-F21)^2+(D9-G21)^2+(D9-H21)^2+(D9-I21)^2</f>
         <v>9.759999999999998</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="22">
         <f t="shared" si="3"/>
         <v>6.4737933238558067</v>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="22">
         <f t="shared" si="4"/>
         <v>1.6462077633154331</v>
       </c>
-      <c r="I28" s="36">
+      <c r="I28" s="22">
         <f t="shared" si="5"/>
         <v>3.1240998703626612</v>
       </c>
-      <c r="J28" s="37" t="str">
+      <c r="J28" s="23" t="str">
         <f t="shared" si="6"/>
         <v>K2</v>
       </c>
-      <c r="K28" s="37" t="str">
+      <c r="K28" s="23" t="str">
         <f t="shared" si="7"/>
         <v>SEDANG</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="20">
+    <row r="29" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="6">
         <v>5</v>
       </c>
-      <c r="C29" s="18" t="str">
+      <c r="C29" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C10</f>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="20">
         <f>(D10-C19)^2+(D10-D19)^2+(D10-E19)^2+(D10-F19)^2+(D10-G19)^2+(D10-H19)^2+(D10-I19)^2</f>
         <v>14.71</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="20">
         <f>(D10-C20)^2+(D10-D20)^2+(D10-E20)^2+(D10-F20)^2+(D10-G20)^2+(D10-H20)^2+(D10-I20)^2</f>
         <v>1.1099999999999994</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="20">
         <f>(D10-C21)^2+(D10-D21)^2+(D10-E21)^2+(D10-F21)^2+(D10-G21)^2+(D10-H21)^2+(D10-I21)^2</f>
         <v>33.159999999999997</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="20">
         <f t="shared" si="3"/>
         <v>3.8353617821530213</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="20">
         <f t="shared" si="4"/>
         <v>1.0535653752852736</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="20">
         <f t="shared" si="5"/>
         <v>5.7584720195551871</v>
       </c>
-      <c r="J29" s="35" t="str">
+      <c r="J29" s="21" t="str">
         <f t="shared" si="6"/>
         <v>K2</v>
       </c>
-      <c r="K29" s="35" t="str">
+      <c r="K29" s="21" t="str">
         <f t="shared" si="7"/>
         <v>SEDANG</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="24">
+    <row r="30" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="10">
         <v>6</v>
       </c>
-      <c r="C30" s="25" t="str">
+      <c r="C30" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C11</f>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="22">
         <f>(D11-C19)^2+(D11-D19)^2+(D11-E19)^2+(D11-F19)^2+(D11-G19)^2+(D11-H19)^2+(D11-I19)^2</f>
         <v>138.31</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="22">
         <f>(D11-C20)^2+(D11-D20)^2+(D11-E20)^2+(D11-F20)^2+(D11-G20)^2+(D11-H20)^2+(D11-I20)^2</f>
         <v>47.91</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="22">
         <f>(D11-C21)^2+(D11-D21)^2+(D11-E21)^2+(D11-F21)^2+(D11-G21)^2+(D11-H21)^2+(D11-I21)^2</f>
         <v>4.9600000000000009</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="22">
         <f t="shared" si="3"/>
         <v>11.760527199067226</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="22">
         <f t="shared" si="4"/>
         <v>6.921704992268884</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="22">
         <f t="shared" si="5"/>
         <v>2.2271057451320089</v>
       </c>
-      <c r="J30" s="37" t="str">
+      <c r="J30" s="23" t="str">
         <f t="shared" si="6"/>
         <v>K3</v>
       </c>
-      <c r="K30" s="37" t="str">
+      <c r="K30" s="23" t="str">
         <f t="shared" si="7"/>
         <v>RENDAH</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="20">
+    <row r="31" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="6">
         <v>7</v>
       </c>
-      <c r="C31" s="18" t="str">
+      <c r="C31" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C12</f>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="20">
         <f>(D12-C19)^2+(D12-D19)^2+(D12-E19)^2+(D12-F19)^2+(D12-G19)^2+(D12-H19)^2+(D12-I19)^2</f>
         <v>2.3099999999999974</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="20">
         <f>(D12-C20)^2+(D12-D20)^2+(D12-E20)^2+(D12-F20)^2+(D12-G20)^2+(D12-H20)^2+(D12-I20)^2</f>
         <v>39.909999999999997</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="20">
         <f>(D12-C21)^2+(D12-D21)^2+(D12-E21)^2+(D12-F21)^2+(D12-G21)^2+(D12-H21)^2+(D12-I21)^2</f>
         <v>121.95999999999998</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="20">
         <f t="shared" si="3"/>
         <v>1.5198684153570654</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="20">
         <f t="shared" si="4"/>
         <v>6.3174361888348347</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="20">
         <f t="shared" si="5"/>
         <v>11.043550153822817</v>
       </c>
-      <c r="J31" s="35" t="str">
+      <c r="J31" s="21" t="str">
         <f t="shared" si="6"/>
         <v>K1</v>
       </c>
-      <c r="K31" s="35" t="str">
+      <c r="K31" s="21" t="str">
         <f t="shared" si="7"/>
         <v>TINGGI</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="24">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="10">
         <v>8</v>
       </c>
-      <c r="C32" s="25" t="str">
+      <c r="C32" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C13</f>
         <v>Hana Putri</v>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="22">
         <f>(D13-C19)^2+(D13-D19)^2+(D13-E19)^2+(D13-F19)^2+(D13-G19)^2+(D13-H19)^2+(D13-I19)^2</f>
         <v>41.910000000000011</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="22">
         <f>(D13-C20)^2+(D13-D20)^2+(D13-E20)^2+(D13-F20)^2+(D13-G20)^2+(D13-H20)^2+(D13-I20)^2</f>
         <v>2.7100000000000009</v>
       </c>
-      <c r="F32" s="36">
+      <c r="F32" s="22">
         <f>(D13-C21)^2+(D13-D21)^2+(D13-E21)^2+(D13-F21)^2+(D13-G21)^2+(D13-H21)^2+(D13-I21)^2</f>
         <v>9.759999999999998</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="22">
         <f t="shared" si="3"/>
         <v>6.4737933238558067</v>
       </c>
-      <c r="H32" s="36">
+      <c r="H32" s="22">
         <f t="shared" si="4"/>
         <v>1.6462077633154331</v>
       </c>
-      <c r="I32" s="36">
+      <c r="I32" s="22">
         <f t="shared" si="5"/>
         <v>3.1240998703626612</v>
       </c>
-      <c r="J32" s="37" t="str">
+      <c r="J32" s="23" t="str">
         <f t="shared" si="6"/>
         <v>K2</v>
       </c>
-      <c r="K32" s="37" t="str">
+      <c r="K32" s="23" t="str">
         <f t="shared" si="7"/>
         <v>SEDANG</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="20">
+    <row r="33" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
         <v>9</v>
       </c>
-      <c r="C33" s="18" t="str">
+      <c r="C33" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C14</f>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="20">
         <f>(D14-C19)^2+(D14-D19)^2+(D14-E19)^2+(D14-F19)^2+(D14-G19)^2+(D14-H19)^2+(D14-I19)^2</f>
         <v>1.5100000000000005</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="20">
         <f>(D14-C20)^2+(D14-D20)^2+(D14-E20)^2+(D14-F20)^2+(D14-G20)^2+(D14-H20)^2+(D14-I20)^2</f>
         <v>13.509999999999998</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="20">
         <f>(D14-C21)^2+(D14-D21)^2+(D14-E21)^2+(D14-F21)^2+(D14-G21)^2+(D14-H21)^2+(D14-I21)^2</f>
         <v>70.56</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="20">
         <f t="shared" si="3"/>
         <v>1.228820572744451</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="20">
         <f t="shared" si="4"/>
         <v>3.675595189897821</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="20">
         <f t="shared" si="5"/>
         <v>8.4</v>
       </c>
-      <c r="J33" s="35" t="str">
+      <c r="J33" s="21" t="str">
         <f t="shared" si="6"/>
         <v>K1</v>
       </c>
-      <c r="K33" s="35" t="str">
+      <c r="K33" s="21" t="str">
         <f t="shared" si="7"/>
         <v>TINGGI</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="24">
+    <row r="34" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="10">
         <v>10</v>
       </c>
-      <c r="C34" s="25" t="str">
+      <c r="C34" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C15</f>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="22">
         <f>(D15-C19)^2+(D15-D19)^2+(D15-E19)^2+(D15-F19)^2+(D15-G19)^2+(D15-H19)^2+(D15-I19)^2</f>
         <v>83.11</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="22">
         <f>(D15-C20)^2+(D15-D20)^2+(D15-E20)^2+(D15-F20)^2+(D15-G20)^2+(D15-H20)^2+(D15-I20)^2</f>
         <v>18.310000000000002</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="22">
         <f>(D15-C21)^2+(D15-D21)^2+(D15-E21)^2+(D15-F21)^2+(D15-G21)^2+(D15-H21)^2+(D15-I21)^2</f>
         <v>0.3599999999999996</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="22">
         <f t="shared" si="3"/>
         <v>9.1164686145458749</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="22">
         <f t="shared" si="4"/>
         <v>4.2790185790669337</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="22">
         <f t="shared" si="5"/>
         <v>0.59999999999999964</v>
       </c>
-      <c r="J34" s="37" t="str">
+      <c r="J34" s="23" t="str">
         <f t="shared" si="6"/>
         <v>K3</v>
       </c>
-      <c r="K34" s="37" t="str">
+      <c r="K34" s="23" t="str">
         <f t="shared" si="7"/>
         <v>RENDAH</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2444,1007 +2444,1007 @@
   <dimension ref="A1:V33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="24" style="15" customWidth="1"/>
-    <col min="3" max="9" width="12" style="15" customWidth="1"/>
-    <col min="10" max="11" width="14" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="9" width="12" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="4" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="2:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="39" t="s">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="14">
         <v>1</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="10">
         <v>3</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="10">
         <v>5</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="10">
         <v>7</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="10">
         <v>7</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="10">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="39" t="s">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="20">
         <f>1/D6</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="14">
         <v>1</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="10">
         <v>3</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="10">
         <v>5</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="10">
         <v>3</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="10">
         <v>5</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="39" t="s">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="20">
         <f>1/E6</f>
         <v>0.2</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="20">
         <f>1/E7</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="14">
         <v>1</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="10">
         <v>3</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="10">
         <v>3</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="20">
         <f>1/F6</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="20">
         <f>1/F7</f>
         <v>0.2</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="20">
         <f>1/F8</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="14">
         <v>1</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="10">
         <v>0.33333333333333298</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="20">
         <f>1/G6</f>
         <v>0.2</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="20">
         <f>1/G7</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="20">
         <f>1/G8</f>
         <v>1</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="20">
         <f>1/G9</f>
         <v>3.0000000000000031</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="14">
         <v>1</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="10">
         <v>3</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="39" t="s">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="20">
         <f>1/H6</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="20">
         <f>1/H7</f>
         <v>0.2</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="20">
         <f>1/H8</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="20">
         <f>1/H9</f>
         <v>1</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="20">
         <f>1/H10</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="14">
         <v>1</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="39" t="s">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="20">
         <f>1/I6</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="20">
         <f>1/I7</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="20">
         <f>1/I8</f>
         <v>0.2</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="20">
         <f>1/I9</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="20">
         <f>1/I10</f>
         <v>0.2</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="20">
         <f>1/I11</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="19" t="s">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="26">
         <f t="shared" ref="C13:I13" si="0">SUM(C6:C12)</f>
         <v>2.1301587301587301</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="26">
         <f t="shared" si="0"/>
         <v>5.2095238095238097</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="26">
         <f t="shared" si="0"/>
         <v>10.866666666666667</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="26">
         <f t="shared" si="0"/>
         <v>20.333333333333336</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="26">
         <f t="shared" si="0"/>
         <v>10.866666666666665</v>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="26">
         <f t="shared" si="0"/>
         <v>20.333333333333332</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="26">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+    </row>
+    <row r="16" spans="2:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="J16" s="27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="39" t="s">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="28">
         <f t="shared" ref="C17:I17" si="1">C6/C13</f>
         <v>0.4694485842026826</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="22">
         <f t="shared" si="1"/>
         <v>0.57586837294332727</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="22">
         <f t="shared" si="1"/>
         <v>0.46012269938650302</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="22">
         <f t="shared" si="1"/>
         <v>0.34426229508196715</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="22">
         <f t="shared" si="1"/>
         <v>0.46012269938650313</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="22">
         <f t="shared" si="1"/>
         <v>0.34426229508196721</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="22">
         <f t="shared" si="1"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="29">
         <f t="shared" ref="J17:J23" si="2">AVERAGE(C17:I17)</f>
         <v>0.41811631697288909</v>
       </c>
-      <c r="P17" s="42">
+      <c r="P17" s="28">
         <f t="shared" ref="P17:V17" si="3">C6/C13</f>
         <v>0.4694485842026826</v>
       </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="22">
         <f t="shared" si="3"/>
         <v>0.57586837294332727</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="22">
         <f t="shared" si="3"/>
         <v>0.46012269938650302</v>
       </c>
-      <c r="S17" s="36">
+      <c r="S17" s="22">
         <f t="shared" si="3"/>
         <v>0.34426229508196715</v>
       </c>
-      <c r="T17" s="36">
+      <c r="T17" s="22">
         <f t="shared" si="3"/>
         <v>0.46012269938650313</v>
       </c>
-      <c r="U17" s="36">
+      <c r="U17" s="22">
         <f t="shared" si="3"/>
         <v>0.34426229508196721</v>
       </c>
-      <c r="V17" s="36">
+      <c r="V17" s="22">
         <f t="shared" si="3"/>
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="18" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="22">
         <f t="shared" ref="C18:I18" si="4">C7/C13</f>
         <v>0.15648286140089418</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="28">
         <f t="shared" si="4"/>
         <v>0.19195612431444239</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="22">
         <f t="shared" si="4"/>
         <v>0.2760736196319018</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="22">
         <f t="shared" si="4"/>
         <v>0.24590163934426226</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="22">
         <f t="shared" si="4"/>
         <v>0.27607361963190186</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="22">
         <f t="shared" si="4"/>
         <v>0.24590163934426232</v>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="22">
         <f t="shared" si="4"/>
         <v>0.21212121212121213</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="29">
         <f t="shared" si="2"/>
         <v>0.22921581654126813</v>
       </c>
-      <c r="P18" s="36">
+      <c r="P18" s="22">
         <f t="shared" ref="P18:V18" si="5">C7/C13</f>
         <v>0.15648286140089418</v>
       </c>
-      <c r="Q18" s="42">
+      <c r="Q18" s="28">
         <f t="shared" si="5"/>
         <v>0.19195612431444239</v>
       </c>
-      <c r="R18" s="36">
+      <c r="R18" s="22">
         <f t="shared" si="5"/>
         <v>0.2760736196319018</v>
       </c>
-      <c r="S18" s="36">
+      <c r="S18" s="22">
         <f t="shared" si="5"/>
         <v>0.24590163934426226</v>
       </c>
-      <c r="T18" s="36">
+      <c r="T18" s="22">
         <f t="shared" si="5"/>
         <v>0.27607361963190186</v>
       </c>
-      <c r="U18" s="36">
+      <c r="U18" s="22">
         <f t="shared" si="5"/>
         <v>0.24590163934426232</v>
       </c>
-      <c r="V18" s="36">
+      <c r="V18" s="22">
         <f t="shared" si="5"/>
         <v>0.21212121212121213</v>
       </c>
     </row>
-    <row r="19" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="22">
         <f t="shared" ref="C19:I19" si="6">C8/C13</f>
         <v>9.3889716840536513E-2</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="22">
         <f t="shared" si="6"/>
         <v>6.3985374771480794E-2</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="28">
         <f t="shared" si="6"/>
         <v>9.202453987730061E-2</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="22">
         <f t="shared" si="6"/>
         <v>0.14754098360655735</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="22">
         <f t="shared" si="6"/>
         <v>9.2024539877300623E-2</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="22">
         <f t="shared" si="6"/>
         <v>0.14754098360655737</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="22">
         <f t="shared" si="6"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="J19" s="43">
+      <c r="J19" s="29">
         <f t="shared" si="2"/>
         <v>0.11264589858498353</v>
       </c>
-      <c r="P19" s="36">
+      <c r="P19" s="22">
         <f t="shared" ref="P19:V19" si="7">C8/C13</f>
         <v>9.3889716840536513E-2</v>
       </c>
-      <c r="Q19" s="36">
+      <c r="Q19" s="22">
         <f t="shared" si="7"/>
         <v>6.3985374771480794E-2</v>
       </c>
-      <c r="R19" s="42">
+      <c r="R19" s="28">
         <f t="shared" si="7"/>
         <v>9.202453987730061E-2</v>
       </c>
-      <c r="S19" s="36">
+      <c r="S19" s="22">
         <f t="shared" si="7"/>
         <v>0.14754098360655735</v>
       </c>
-      <c r="T19" s="36">
+      <c r="T19" s="22">
         <f t="shared" si="7"/>
         <v>9.2024539877300623E-2</v>
       </c>
-      <c r="U19" s="36">
+      <c r="U19" s="22">
         <f t="shared" si="7"/>
         <v>0.14754098360655737</v>
       </c>
-      <c r="V19" s="36">
+      <c r="V19" s="22">
         <f t="shared" si="7"/>
         <v>0.15151515151515152</v>
       </c>
     </row>
-    <row r="20" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="39" t="s">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B20" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="22">
         <f t="shared" ref="C20:I20" si="8">C9/C13</f>
         <v>6.7064083457526083E-2</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="22">
         <f t="shared" si="8"/>
         <v>3.8391224862888484E-2</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="22">
         <f t="shared" si="8"/>
         <v>3.0674846625766868E-2</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="28">
         <f t="shared" si="8"/>
         <v>4.9180327868852451E-2</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="22">
         <f t="shared" si="8"/>
         <v>3.0674846625766843E-2</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="22">
         <f t="shared" si="8"/>
         <v>4.9180327868852465E-2</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="22">
         <f t="shared" si="8"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="J20" s="43">
+      <c r="J20" s="29">
         <f t="shared" si="2"/>
         <v>5.0867821174106299E-2</v>
       </c>
-      <c r="P20" s="36">
+      <c r="P20" s="22">
         <f t="shared" ref="P20:V20" si="9">C9/C13</f>
         <v>6.7064083457526083E-2</v>
       </c>
-      <c r="Q20" s="36">
+      <c r="Q20" s="22">
         <f t="shared" si="9"/>
         <v>3.8391224862888484E-2</v>
       </c>
-      <c r="R20" s="36">
+      <c r="R20" s="22">
         <f t="shared" si="9"/>
         <v>3.0674846625766868E-2</v>
       </c>
-      <c r="S20" s="42">
+      <c r="S20" s="28">
         <f t="shared" si="9"/>
         <v>4.9180327868852451E-2</v>
       </c>
-      <c r="T20" s="36">
+      <c r="T20" s="22">
         <f t="shared" si="9"/>
         <v>3.0674846625766843E-2</v>
       </c>
-      <c r="U20" s="36">
+      <c r="U20" s="22">
         <f t="shared" si="9"/>
         <v>4.9180327868852465E-2</v>
       </c>
-      <c r="V20" s="36">
+      <c r="V20" s="22">
         <f t="shared" si="9"/>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="39" t="s">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="22">
         <f t="shared" ref="C21:I21" si="10">C10/C13</f>
         <v>9.3889716840536513E-2</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="22">
         <f t="shared" si="10"/>
         <v>6.3985374771480794E-2</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="22">
         <f t="shared" si="10"/>
         <v>9.202453987730061E-2</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="22">
         <f t="shared" si="10"/>
         <v>0.14754098360655751</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="28">
         <f t="shared" si="10"/>
         <v>9.2024539877300623E-2</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="22">
         <f t="shared" si="10"/>
         <v>0.14754098360655737</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="22">
         <f t="shared" si="10"/>
         <v>0.15151515151515152</v>
       </c>
-      <c r="J21" s="43">
+      <c r="J21" s="29">
         <f t="shared" si="2"/>
         <v>0.11264589858498356</v>
       </c>
-      <c r="P21" s="36">
+      <c r="P21" s="22">
         <f t="shared" ref="P21:V21" si="11">C10/C13</f>
         <v>9.3889716840536513E-2</v>
       </c>
-      <c r="Q21" s="36">
+      <c r="Q21" s="22">
         <f t="shared" si="11"/>
         <v>6.3985374771480794E-2</v>
       </c>
-      <c r="R21" s="36">
+      <c r="R21" s="22">
         <f t="shared" si="11"/>
         <v>9.202453987730061E-2</v>
       </c>
-      <c r="S21" s="36">
+      <c r="S21" s="22">
         <f t="shared" si="11"/>
         <v>0.14754098360655751</v>
       </c>
-      <c r="T21" s="42">
+      <c r="T21" s="28">
         <f t="shared" si="11"/>
         <v>9.2024539877300623E-2</v>
       </c>
-      <c r="U21" s="36">
+      <c r="U21" s="22">
         <f t="shared" si="11"/>
         <v>0.14754098360655737</v>
       </c>
-      <c r="V21" s="36">
+      <c r="V21" s="22">
         <f t="shared" si="11"/>
         <v>0.15151515151515152</v>
       </c>
     </row>
-    <row r="22" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="39" t="s">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="22">
         <f t="shared" ref="C22:I22" si="12">C11/C13</f>
         <v>6.7064083457526083E-2</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="22">
         <f t="shared" si="12"/>
         <v>3.8391224862888484E-2</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="22">
         <f t="shared" si="12"/>
         <v>3.0674846625766868E-2</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="22">
         <f t="shared" si="12"/>
         <v>4.9180327868852451E-2</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="22">
         <f t="shared" si="12"/>
         <v>3.0674846625766874E-2</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="28">
         <f t="shared" si="12"/>
         <v>4.9180327868852465E-2</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="22">
         <f t="shared" si="12"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="J22" s="43">
+      <c r="J22" s="29">
         <f t="shared" si="2"/>
         <v>5.0867821174106313E-2</v>
       </c>
-      <c r="P22" s="36">
+      <c r="P22" s="22">
         <f t="shared" ref="P22:V22" si="13">C11/C13</f>
         <v>6.7064083457526083E-2</v>
       </c>
-      <c r="Q22" s="36">
+      <c r="Q22" s="22">
         <f t="shared" si="13"/>
         <v>3.8391224862888484E-2</v>
       </c>
-      <c r="R22" s="36">
+      <c r="R22" s="22">
         <f t="shared" si="13"/>
         <v>3.0674846625766868E-2</v>
       </c>
-      <c r="S22" s="36">
+      <c r="S22" s="22">
         <f t="shared" si="13"/>
         <v>4.9180327868852451E-2</v>
       </c>
-      <c r="T22" s="36">
+      <c r="T22" s="22">
         <f t="shared" si="13"/>
         <v>3.0674846625766874E-2</v>
       </c>
-      <c r="U22" s="42">
+      <c r="U22" s="28">
         <f t="shared" si="13"/>
         <v>4.9180327868852465E-2</v>
       </c>
-      <c r="V22" s="36">
+      <c r="V22" s="22">
         <f t="shared" si="13"/>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="39" t="s">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="22">
         <f t="shared" ref="C23:I23" si="14">C12/C13</f>
         <v>5.216095380029806E-2</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="22">
         <f t="shared" si="14"/>
         <v>2.7422303473491772E-2</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="22">
         <f t="shared" si="14"/>
         <v>1.8404907975460124E-2</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="22">
         <f t="shared" si="14"/>
         <v>1.6393442622950817E-2</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="22">
         <f t="shared" si="14"/>
         <v>1.8404907975460127E-2</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="22">
         <f t="shared" si="14"/>
         <v>1.6393442622950821E-2</v>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="28">
         <f t="shared" si="14"/>
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="J23" s="43">
+      <c r="J23" s="29">
         <f t="shared" si="2"/>
         <v>2.5640426967663145E-2</v>
       </c>
-      <c r="P23" s="36">
+      <c r="P23" s="22">
         <f t="shared" ref="P23:V23" si="15">C12/C13</f>
         <v>5.216095380029806E-2</v>
       </c>
-      <c r="Q23" s="36">
+      <c r="Q23" s="22">
         <f t="shared" si="15"/>
         <v>2.7422303473491772E-2</v>
       </c>
-      <c r="R23" s="36">
+      <c r="R23" s="22">
         <f t="shared" si="15"/>
         <v>1.8404907975460124E-2</v>
       </c>
-      <c r="S23" s="36">
+      <c r="S23" s="22">
         <f t="shared" si="15"/>
         <v>1.6393442622950817E-2</v>
       </c>
-      <c r="T23" s="36">
+      <c r="T23" s="22">
         <f t="shared" si="15"/>
         <v>1.8404907975460127E-2</v>
       </c>
-      <c r="U23" s="36">
+      <c r="U23" s="22">
         <f t="shared" si="15"/>
         <v>1.6393442622950821E-2</v>
       </c>
-      <c r="V23" s="42">
+      <c r="V23" s="28">
         <f t="shared" si="15"/>
         <v>3.0303030303030304E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-    </row>
-    <row r="26" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="19" t="s">
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+    </row>
+    <row r="26" spans="2:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="30">
         <f>C6*J17+D6*J18+E6*J19+F6*J20+G6*J21+H6*J22+I6*J23</f>
         <v>3.1751360915929854</v>
       </c>
-      <c r="D26" s="44">
+      <c r="D26" s="30">
         <f>C7*J17+D7*J18+E7*J19+F7*J20+G7*J21+H7*J22+I7*J23</f>
         <v>1.7326245142235042</v>
       </c>
-      <c r="E26" s="44">
+      <c r="E26" s="30">
         <f>C8*J17+D8*J18+E8*J19+F8*J20+G8*J21+H8*J22+I8*J23</f>
         <v>0.81872939462792105</v>
       </c>
-      <c r="F26" s="44">
+      <c r="F26" s="30">
         <f>C9*J17+D9*J18+E9*J19+F9*J20+G9*J21+H9*J22+I9*J23</f>
         <v>0.35932825470747642</v>
       </c>
-      <c r="G26" s="44">
+      <c r="G26" s="30">
         <f>C10*J17+D10*J18+E10*J19+F10*J20+G10*J21+H10*J22+I10*J23</f>
         <v>0.81872939462792127</v>
       </c>
-      <c r="H26" s="44">
+      <c r="H26" s="30">
         <f>C11*J17+D11*J18+E11*J19+F11*J20+G11*J21+H11*J22+I11*J23</f>
         <v>0.35932825470747648</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="30">
         <f>C12*J17+D12*J18+E12*J19+F12*J20+G12*J21+H12*J22+I12*J23</f>
         <v>0.18381315238568993</v>
       </c>
     </row>
-    <row r="27" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
+    <row r="27" spans="2:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="20">
         <f>C26/J17</f>
         <v>7.5939061995489237</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="20">
         <f>D26/J18</f>
         <v>7.558922156279567</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="20">
         <f>E26/J19</f>
         <v>7.2681687030997084</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="20">
         <f>F26/J20</f>
         <v>7.0639600127081614</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="20">
         <f>G26/J21</f>
         <v>7.2681687030997093</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="20">
         <f>H26/J22</f>
         <v>7.0639600127081605</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="20">
         <f>I26/J23</f>
         <v>7.1688803239317727</v>
       </c>
     </row>
-    <row r="28" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B28" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-    </row>
-    <row r="29" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B29" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="63">
         <f>AVERAGE(C27:I27)</f>
         <v>7.2837094444822856</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="45" t="s">
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="63"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="63">
         <f>(C29-C28)/(C28-1)</f>
         <v>4.7284907413714272E-2</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B31" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="63">
         <v>1.32</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="45" t="s">
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="63">
         <f>C30/C31</f>
         <v>3.5821899555844146E-2</v>
       </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="45" t="s">
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="6" t="str">
+      <c r="C33" s="61" t="str">
         <f>IF(C32&lt;0.1,"✔ KONSISTEN (CR &lt; 0.1)","✘ TIDAK KONSISTEN")</f>
         <v>✔ KONSISTEN (CR &lt; 0.1)</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B25:K25"/>
     <mergeCell ref="C33:K33"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C29:K29"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C31:K31"/>
     <mergeCell ref="C32:K32"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="B25:K25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3456,684 +3456,684 @@
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="9" width="11" style="15" customWidth="1"/>
-    <col min="10" max="10" width="16" style="15" customWidth="1"/>
-    <col min="11" max="11" width="10" style="15" customWidth="1"/>
-    <col min="12" max="12" width="12" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
     </row>
     <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="29">
         <f>'TAHAP 2 – AHP'!J17</f>
         <v>0.41811631697288909</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="29">
         <f>'TAHAP 2 – AHP'!J18</f>
         <v>0.22921581654126813</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="29">
         <f>'TAHAP 2 – AHP'!J19</f>
         <v>0.11264589858498353</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="29">
         <f>'TAHAP 2 – AHP'!J20</f>
         <v>5.0867821174106299E-2</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="29">
         <f>'TAHAP 2 – AHP'!J21</f>
         <v>0.11264589858498356</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="29">
         <f>'TAHAP 2 – AHP'!J22</f>
         <v>5.0867821174106313E-2</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="29">
         <f>'TAHAP 2 – AHP'!J23</f>
         <v>2.5640426967663145E-2</v>
       </c>
     </row>
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
     </row>
     <row r="8" spans="2:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="20">
+      <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="18" t="str">
+      <c r="C9" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C6</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="33">
         <f>'TAHAP 1 – K-MEANS'!D6</f>
         <v>8</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="33">
         <f>'TAHAP 1 – K-MEANS'!E6</f>
         <v>7</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="33">
         <f>'TAHAP 1 – K-MEANS'!F6</f>
         <v>9</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="33">
         <f>'TAHAP 1 – K-MEANS'!G6</f>
         <v>8</v>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="33">
         <f>'TAHAP 1 – K-MEANS'!H6</f>
         <v>9</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="33">
         <f>'TAHAP 1 – K-MEANS'!I6</f>
         <v>7</v>
       </c>
-      <c r="J9" s="47">
+      <c r="J9" s="33">
         <f>'TAHAP 1 – K-MEANS'!J6</f>
         <v>8</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="29">
         <f>(D9^C6)*(E9^D6)*(F9^E6)*(G9^F6)*(H9^G6)*(I9^H6)*(J9^I6)</f>
         <v>7.9135551847656185</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="7">
         <f>RANK(K9,K9:K18,0)</f>
         <v>4</v>
       </c>
-      <c r="M9" s="35" t="str">
+      <c r="M9" s="21" t="str">
         <f>'TAHAP 1 – K-MEANS'!M6</f>
         <v>K1</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="24">
+      <c r="B10" s="10">
         <v>2</v>
       </c>
-      <c r="C10" s="25" t="str">
+      <c r="C10" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C7</f>
         <v>Budi Santoso</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="34">
         <f>'TAHAP 1 – K-MEANS'!D7</f>
         <v>5</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="34">
         <f>'TAHAP 1 – K-MEANS'!E7</f>
         <v>6</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="34">
         <f>'TAHAP 1 – K-MEANS'!F7</f>
         <v>5</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="34">
         <f>'TAHAP 1 – K-MEANS'!G7</f>
         <v>6</v>
       </c>
-      <c r="H10" s="48">
+      <c r="H10" s="34">
         <f>'TAHAP 1 – K-MEANS'!H7</f>
         <v>5</v>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="34">
         <f>'TAHAP 1 – K-MEANS'!I7</f>
         <v>6</v>
       </c>
-      <c r="J10" s="48">
+      <c r="J10" s="34">
         <f>'TAHAP 1 – K-MEANS'!J7</f>
         <v>5</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="29">
         <f>(D10^C6)*(E10^D6)*(F10^E6)*(G10^F6)*(H10^G6)*(I10^H6)*(J10^I6)</f>
         <v>5.3109859588063157</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="12">
         <f>RANK(K10,K9:K18,0)</f>
         <v>8</v>
       </c>
-      <c r="M10" s="37" t="str">
+      <c r="M10" s="23" t="str">
         <f>'TAHAP 1 – K-MEANS'!M7</f>
         <v>K3</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="20">
+      <c r="B11" s="6">
         <v>3</v>
       </c>
-      <c r="C11" s="18" t="str">
+      <c r="C11" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C8</f>
         <v>Citra Dewi</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="33">
         <f>'TAHAP 1 – K-MEANS'!D8</f>
         <v>9</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="33">
         <f>'TAHAP 1 – K-MEANS'!E8</f>
         <v>9</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="33">
         <f>'TAHAP 1 – K-MEANS'!F8</f>
         <v>8</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="33">
         <f>'TAHAP 1 – K-MEANS'!G8</f>
         <v>9</v>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="33">
         <f>'TAHAP 1 – K-MEANS'!H8</f>
         <v>9</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="33">
         <f>'TAHAP 1 – K-MEANS'!I8</f>
         <v>8</v>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="33">
         <f>'TAHAP 1 – K-MEANS'!J8</f>
         <v>9</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="29">
         <f>(D11^C6)*(E11^D6)*(F11^E6)*(G11^F6)*(H11^G6)*(I11^H6)*(J11^I6)</f>
         <v>8.8283261711137531</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="7">
         <f>RANK(K11,K9:K18,0)</f>
         <v>1</v>
       </c>
-      <c r="M11" s="35" t="str">
+      <c r="M11" s="21" t="str">
         <f>'TAHAP 1 – K-MEANS'!M8</f>
         <v>K1</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="24">
+      <c r="B12" s="10">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="str">
+      <c r="C12" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C9</f>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="34">
         <f>'TAHAP 1 – K-MEANS'!D9</f>
         <v>6</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="34">
         <f>'TAHAP 1 – K-MEANS'!E9</f>
         <v>5</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="34">
         <f>'TAHAP 1 – K-MEANS'!F9</f>
         <v>6</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="34">
         <f>'TAHAP 1 – K-MEANS'!G9</f>
         <v>5</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="34">
         <f>'TAHAP 1 – K-MEANS'!H9</f>
         <v>6</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="34">
         <f>'TAHAP 1 – K-MEANS'!I9</f>
         <v>5</v>
       </c>
-      <c r="J12" s="48">
+      <c r="J12" s="34">
         <f>'TAHAP 1 – K-MEANS'!J9</f>
         <v>6</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="29">
         <f>(D12^C6)*(E12^D6)*(F12^E6)*(G12^F6)*(H12^G6)*(I12^H6)*(J12^I6)</f>
         <v>5.6486686714462202</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="12">
         <f>RANK(K12,K9:K18,0)</f>
         <v>7</v>
       </c>
-      <c r="M12" s="37" t="str">
+      <c r="M12" s="23" t="str">
         <f>'TAHAP 1 – K-MEANS'!M9</f>
         <v>K2</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="20">
+      <c r="B13" s="6">
         <v>5</v>
       </c>
-      <c r="C13" s="18" t="str">
+      <c r="C13" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C10</f>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="33">
         <f>'TAHAP 1 – K-MEANS'!D10</f>
         <v>7</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="33">
         <f>'TAHAP 1 – K-MEANS'!E10</f>
         <v>8</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="33">
         <f>'TAHAP 1 – K-MEANS'!F10</f>
         <v>7</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="33">
         <f>'TAHAP 1 – K-MEANS'!G10</f>
         <v>8</v>
       </c>
-      <c r="H13" s="47">
+      <c r="H13" s="33">
         <f>'TAHAP 1 – K-MEANS'!H10</f>
         <v>7</v>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="33">
         <f>'TAHAP 1 – K-MEANS'!I10</f>
         <v>8</v>
       </c>
-      <c r="J13" s="47">
+      <c r="J13" s="33">
         <f>'TAHAP 1 – K-MEANS'!J10</f>
         <v>7</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="29">
         <f>(D13^C6)*(E13^D6)*(F13^E6)*(G13^F6)*(H13^G6)*(I13^H6)*(J13^I6)</f>
         <v>7.3162840691386792</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="7">
         <f>RANK(K13,K9:K18,0)</f>
         <v>5</v>
       </c>
-      <c r="M13" s="35" t="str">
+      <c r="M13" s="21" t="str">
         <f>'TAHAP 1 – K-MEANS'!M10</f>
         <v>K2</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="24">
+      <c r="B14" s="10">
         <v>6</v>
       </c>
-      <c r="C14" s="25" t="str">
+      <c r="C14" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C11</f>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="34">
         <f>'TAHAP 1 – K-MEANS'!D11</f>
         <v>4</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="34">
         <f>'TAHAP 1 – K-MEANS'!E11</f>
         <v>5</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="34">
         <f>'TAHAP 1 – K-MEANS'!F11</f>
         <v>4</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="34">
         <f>'TAHAP 1 – K-MEANS'!G11</f>
         <v>5</v>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="34">
         <f>'TAHAP 1 – K-MEANS'!H11</f>
         <v>4</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="34">
         <f>'TAHAP 1 – K-MEANS'!I11</f>
         <v>5</v>
       </c>
-      <c r="J14" s="48">
+      <c r="J14" s="34">
         <f>'TAHAP 1 – K-MEANS'!J11</f>
         <v>4</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="29">
         <f>(D14^C6)*(E14^D6)*(F14^E6)*(G14^F6)*(H14^G6)*(I14^H6)*(J14^I6)</f>
         <v>4.3065798248266693</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="12">
         <f>RANK(K14,K9:K18,0)</f>
         <v>10</v>
       </c>
-      <c r="M14" s="37" t="str">
+      <c r="M14" s="23" t="str">
         <f>'TAHAP 1 – K-MEANS'!M11</f>
         <v>K3</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="20">
+      <c r="B15" s="6">
         <v>7</v>
       </c>
-      <c r="C15" s="18" t="str">
+      <c r="C15" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C12</f>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="33">
         <f>'TAHAP 1 – K-MEANS'!D12</f>
         <v>9</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="33">
         <f>'TAHAP 1 – K-MEANS'!E12</f>
         <v>8</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="33">
         <f>'TAHAP 1 – K-MEANS'!F12</f>
         <v>9</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="33">
         <f>'TAHAP 1 – K-MEANS'!G12</f>
         <v>9</v>
       </c>
-      <c r="H15" s="47">
+      <c r="H15" s="33">
         <f>'TAHAP 1 – K-MEANS'!H12</f>
         <v>8</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="33">
         <f>'TAHAP 1 – K-MEANS'!I12</f>
         <v>9</v>
       </c>
-      <c r="J15" s="47">
+      <c r="J15" s="33">
         <f>'TAHAP 1 – K-MEANS'!J12</f>
         <v>8</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="29">
         <f>(D15^C6)*(E15^D6)*(F15^E6)*(G15^F6)*(H15^G6)*(I15^H6)*(J15^I6)</f>
         <v>8.6187413542836833</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="7">
         <f>RANK(K15,K9:K18,0)</f>
         <v>2</v>
       </c>
-      <c r="M15" s="35" t="str">
+      <c r="M15" s="21" t="str">
         <f>'TAHAP 1 – K-MEANS'!M12</f>
         <v>K1</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="24">
+      <c r="B16" s="10">
         <v>8</v>
       </c>
-      <c r="C16" s="25" t="str">
+      <c r="C16" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C13</f>
         <v>Hana Putri</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="34">
         <f>'TAHAP 1 – K-MEANS'!D13</f>
         <v>6</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="34">
         <f>'TAHAP 1 – K-MEANS'!E13</f>
         <v>6</v>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="34">
         <f>'TAHAP 1 – K-MEANS'!F13</f>
         <v>7</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="34">
         <f>'TAHAP 1 – K-MEANS'!G13</f>
         <v>6</v>
       </c>
-      <c r="H16" s="48">
+      <c r="H16" s="34">
         <f>'TAHAP 1 – K-MEANS'!H13</f>
         <v>7</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="34">
         <f>'TAHAP 1 – K-MEANS'!I13</f>
         <v>6</v>
       </c>
-      <c r="J16" s="48">
+      <c r="J16" s="34">
         <f>'TAHAP 1 – K-MEANS'!J13</f>
         <v>7</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="29">
         <f>(D16^C6)*(E16^D6)*(F16^E6)*(G16^F6)*(H16^G6)*(I16^H6)*(J16^I6)</f>
         <v>6.2366354244847422</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="12">
         <f>RANK(K16,K9:K18,0)</f>
         <v>6</v>
       </c>
-      <c r="M16" s="37" t="str">
+      <c r="M16" s="23" t="str">
         <f>'TAHAP 1 – K-MEANS'!M13</f>
         <v>K2</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="20">
+      <c r="B17" s="6">
         <v>9</v>
       </c>
-      <c r="C17" s="18" t="str">
+      <c r="C17" s="4" t="str">
         <f>'TAHAP 1 – K-MEANS'!C14</f>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="33">
         <f>'TAHAP 1 – K-MEANS'!D14</f>
         <v>8</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="33">
         <f>'TAHAP 1 – K-MEANS'!E14</f>
         <v>9</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="33">
         <f>'TAHAP 1 – K-MEANS'!F14</f>
         <v>8</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="33">
         <f>'TAHAP 1 – K-MEANS'!G14</f>
         <v>8</v>
       </c>
-      <c r="H17" s="47">
+      <c r="H17" s="33">
         <f>'TAHAP 1 – K-MEANS'!H14</f>
         <v>9</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="33">
         <f>'TAHAP 1 – K-MEANS'!I14</f>
         <v>9</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="33">
         <f>'TAHAP 1 – K-MEANS'!J14</f>
         <v>8</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="29">
         <f>(D17^C6)*(E17^D6)*(F17^E6)*(G17^F6)*(H17^G6)*(I17^H6)*(J17^I6)</f>
         <v>8.3787473185254893</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="7">
         <f>RANK(K17,K9:K18,0)</f>
         <v>3</v>
       </c>
-      <c r="M17" s="35" t="str">
+      <c r="M17" s="21" t="str">
         <f>'TAHAP 1 – K-MEANS'!M14</f>
         <v>K1</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="24">
+      <c r="B18" s="10">
         <v>10</v>
       </c>
-      <c r="C18" s="25" t="str">
+      <c r="C18" s="11" t="str">
         <f>'TAHAP 1 – K-MEANS'!C15</f>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="34">
         <f>'TAHAP 1 – K-MEANS'!D15</f>
         <v>5</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="34">
         <f>'TAHAP 1 – K-MEANS'!E15</f>
         <v>4</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="34">
         <f>'TAHAP 1 – K-MEANS'!F15</f>
         <v>5</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="34">
         <f>'TAHAP 1 – K-MEANS'!G15</f>
         <v>4</v>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="34">
         <f>'TAHAP 1 – K-MEANS'!H15</f>
         <v>5</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="34">
         <f>'TAHAP 1 – K-MEANS'!I15</f>
         <v>4</v>
       </c>
-      <c r="J18" s="48">
+      <c r="J18" s="34">
         <f>'TAHAP 1 – K-MEANS'!J15</f>
         <v>5</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18" s="29">
         <f>(D18^C6)*(E18^D6)*(F18^E6)*(G18^F6)*(H18^G6)*(I18^H6)*(J18^I6)</f>
         <v>4.6440564934390753</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="12">
         <f>RANK(K18,K9:K18,0)</f>
         <v>9</v>
       </c>
-      <c r="M18" s="37" t="str">
+      <c r="M18" s="23" t="str">
         <f>'TAHAP 1 – K-MEANS'!M15</f>
         <v>K3</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4153,1501 +4153,1501 @@
   <dimension ref="A1:O47"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="9" width="10" style="15" customWidth="1"/>
-    <col min="10" max="11" width="12" style="15" customWidth="1"/>
-    <col min="12" max="12" width="14" style="15" customWidth="1"/>
-    <col min="13" max="13" width="10" style="15" customWidth="1"/>
-    <col min="14" max="14" width="12" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="9" width="10" style="1" customWidth="1"/>
+    <col min="10" max="11" width="12" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
     </row>
     <row r="2" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
     </row>
     <row r="4" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
     </row>
     <row r="5" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="20">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="str">
+      <c r="C6" s="4" t="str">
         <f>'TAHAP 3 – WP'!C9</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="20">
         <f>'TAHAP 3 – WP'!D9/C16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="20">
         <f>'TAHAP 3 – WP'!E9/D16</f>
         <v>0.32050798254694107</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="20">
         <f>'TAHAP 3 – WP'!F9/E16</f>
         <v>0.40657855630736306</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="20">
         <f>'TAHAP 3 – WP'!G9/F16</f>
         <v>0.36066785386697292</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="20">
         <f>'TAHAP 3 – WP'!H9/G16</f>
         <v>0.39970403251589481</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="20">
         <f>'TAHAP 3 – WP'!I9/H16</f>
         <v>0.32050798254694107</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="20">
         <f>'TAHAP 3 – WP'!J9/I16</f>
         <v>0.36784039189736228</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="35">
         <f>SQRT((D20-D30)^2+(E20-E30)^2+(F20-F30)^2+(G20-G30)^2+(H20-H30)^2+(I20-I30)^2+(J20-J30)^2)</f>
         <v>2.8903896126459227E-2</v>
       </c>
-      <c r="L6" s="50">
+      <c r="L6" s="36">
         <f>SQRT((D20-D31)^2+(E20-E31)^2+(F20-F31)^2+(G20-G31)^2+(H20-H31)^2+(I20-I31)^2+(J20-J31)^2)</f>
         <v>9.1014558046647612E-2</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="29">
         <f t="shared" ref="M6:M15" si="0">L6/(K6+L6)</f>
         <v>0.75897040763437995</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="7">
         <f>RANK(M6,M6:M15,0)</f>
         <v>4</v>
       </c>
-      <c r="O6" s="51" t="str">
+      <c r="O6" s="37" t="str">
         <f>'TAHAP 3 – WP'!M9</f>
         <v>K1</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24">
+      <c r="B7" s="10">
         <v>2</v>
       </c>
-      <c r="C7" s="25" t="str">
+      <c r="C7" s="11" t="str">
         <f>'TAHAP 3 – WP'!C10</f>
         <v>Budi Santoso</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="22">
         <f>'TAHAP 3 – WP'!D10/C16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="22">
         <f>'TAHAP 3 – WP'!E10/D16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="22">
         <f>'TAHAP 3 – WP'!F10/E16</f>
         <v>0.22587697572631282</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="22">
         <f>'TAHAP 3 – WP'!G10/F16</f>
         <v>0.27050089040022968</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="22">
         <f>'TAHAP 3 – WP'!H10/G16</f>
         <v>0.22205779584216379</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="22">
         <f>'TAHAP 3 – WP'!I10/H16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="22">
         <f>'TAHAP 3 – WP'!J10/I16</f>
         <v>0.22990024493585143</v>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="35">
         <f>SQRT((D21-D30)^2+(E21-E30)^2+(F21-F30)^2+(G21-G30)^2+(H21-H30)^2+(I21-I30)^2+(J21-J30)^2)</f>
         <v>8.8252591509920209E-2</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="36">
         <f>SQRT((D21-D31)^2+(E21-E31)^2+(F21-F31)^2+(G21-G31)^2+(H21-H31)^2+(I21-I31)^2+(J21-J31)^2)</f>
         <v>3.0035592088194722E-2</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="29">
         <f t="shared" si="0"/>
         <v>0.25391878693683295</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="7">
         <f>RANK(M7,M6:M15,0)</f>
         <v>8</v>
       </c>
-      <c r="O7" s="51" t="str">
+      <c r="O7" s="37" t="str">
         <f>'TAHAP 3 – WP'!M10</f>
         <v>K3</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="20">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="18" t="str">
+      <c r="C8" s="4" t="str">
         <f>'TAHAP 3 – WP'!C11</f>
         <v>Citra Dewi</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="20">
         <f>'TAHAP 3 – WP'!D11/C16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="20">
         <f>'TAHAP 3 – WP'!E11/D16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="20">
         <f>'TAHAP 3 – WP'!F11/E16</f>
         <v>0.36140316116210053</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="20">
         <f>'TAHAP 3 – WP'!G11/F16</f>
         <v>0.40575133560034449</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="20">
         <f>'TAHAP 3 – WP'!H11/G16</f>
         <v>0.39970403251589481</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="20">
         <f>'TAHAP 3 – WP'!I11/H16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="20">
         <f>'TAHAP 3 – WP'!J11/I16</f>
         <v>0.41382044088453257</v>
       </c>
-      <c r="K8" s="49">
+      <c r="K8" s="35">
         <f>SQRT((D22-D30)^2+(E22-E30)^2+(F22-F30)^2+(G22-G30)^2+(H22-H30)^2+(I22-I30)^2+(J22-J30)^2)</f>
         <v>5.5964918908110476E-3</v>
       </c>
-      <c r="L8" s="50">
+      <c r="L8" s="36">
         <f>SQRT((D22-D31)^2+(E22-E31)^2+(F22-F31)^2+(G22-G31)^2+(H22-H31)^2+(I22-I31)^2+(J22-J31)^2)</f>
         <v>0.11493153492383669</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="29">
         <f t="shared" si="0"/>
         <v>0.95356688366418274</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="7">
         <f>RANK(M8,M6:M15,0)</f>
         <v>1</v>
       </c>
-      <c r="O8" s="51" t="str">
+      <c r="O8" s="37" t="str">
         <f>'TAHAP 3 – WP'!M11</f>
         <v>K1</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24">
+      <c r="B9" s="10">
         <v>4</v>
       </c>
-      <c r="C9" s="25" t="str">
+      <c r="C9" s="11" t="str">
         <f>'TAHAP 3 – WP'!C12</f>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="22">
         <f>'TAHAP 3 – WP'!D12/C16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="22">
         <f>'TAHAP 3 – WP'!E12/D16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="22">
         <f>'TAHAP 3 – WP'!F12/E16</f>
         <v>0.27105237087157541</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="22">
         <f>'TAHAP 3 – WP'!G12/F16</f>
         <v>0.22541740866685805</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="22">
         <f>'TAHAP 3 – WP'!H12/G16</f>
         <v>0.26646935501059654</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="22">
         <f>'TAHAP 3 – WP'!I12/H16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="22">
         <f>'TAHAP 3 – WP'!J12/I16</f>
         <v>0.27588029392302171</v>
       </c>
-      <c r="K9" s="49">
+      <c r="K9" s="35">
         <f>SQRT((D23-D30)^2+(E23-E30)^2+(F23-F30)^2+(G23-G30)^2+(H23-H30)^2+(I23-I30)^2+(J23-J30)^2)</f>
         <v>7.5515722237739863E-2</v>
       </c>
-      <c r="L9" s="50">
+      <c r="L9" s="36">
         <f>SQRT((D23-D31)^2+(E23-E31)^2+(F23-F31)^2+(G23-G31)^2+(H23-H31)^2+(I23-I31)^2+(J23-J31)^2)</f>
         <v>4.2380326220693938E-2</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="29">
         <f t="shared" si="0"/>
         <v>0.35947198209646375</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="7">
         <f>RANK(M9,M6:M15,0)</f>
         <v>7</v>
       </c>
-      <c r="O9" s="51" t="str">
+      <c r="O9" s="37" t="str">
         <f>'TAHAP 3 – WP'!M12</f>
         <v>K2</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="20">
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="18" t="str">
+      <c r="C10" s="4" t="str">
         <f>'TAHAP 3 – WP'!C13</f>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="20">
         <f>'TAHAP 3 – WP'!D13/C16</f>
         <v>0.32050798254694107</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="20">
         <f>'TAHAP 3 – WP'!E13/D16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="20">
         <f>'TAHAP 3 – WP'!F13/E16</f>
         <v>0.31622776601683794</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="20">
         <f>'TAHAP 3 – WP'!G13/F16</f>
         <v>0.36066785386697292</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="20">
         <f>'TAHAP 3 – WP'!H13/G16</f>
         <v>0.3108809141790293</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="20">
         <f>'TAHAP 3 – WP'!I13/H16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="20">
         <f>'TAHAP 3 – WP'!J13/I16</f>
         <v>0.321860342910192</v>
       </c>
-      <c r="K10" s="49">
+      <c r="K10" s="35">
         <f>SQRT((D24-D30)^2+(E24-E30)^2+(F24-F30)^2+(G24-G30)^2+(H24-H30)^2+(I24-I30)^2+(J24-J30)^2)</f>
         <v>4.2380326220693938E-2</v>
       </c>
-      <c r="L10" s="50">
+      <c r="L10" s="36">
         <f>SQRT((D24-D31)^2+(E24-E31)^2+(F24-F31)^2+(G24-G31)^2+(H24-H31)^2+(I24-I31)^2+(J24-J31)^2)</f>
         <v>7.5515722237739849E-2</v>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="29">
         <f t="shared" si="0"/>
         <v>0.6405280179035362</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="7">
         <f>RANK(M10,M6:M15,0)</f>
         <v>5</v>
       </c>
-      <c r="O10" s="51" t="str">
+      <c r="O10" s="37" t="str">
         <f>'TAHAP 3 – WP'!M13</f>
         <v>K2</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24">
+      <c r="B11" s="10">
         <v>6</v>
       </c>
-      <c r="C11" s="25" t="str">
+      <c r="C11" s="11" t="str">
         <f>'TAHAP 3 – WP'!C14</f>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="22">
         <f>'TAHAP 3 – WP'!D14/C16</f>
         <v>0.18314741859825204</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="22">
         <f>'TAHAP 3 – WP'!E14/D16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="22">
         <f>'TAHAP 3 – WP'!F14/E16</f>
         <v>0.18070158058105026</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="22">
         <f>'TAHAP 3 – WP'!G14/F16</f>
         <v>0.22541740866685805</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="22">
         <f>'TAHAP 3 – WP'!H14/G16</f>
         <v>0.17764623667373103</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="22">
         <f>'TAHAP 3 – WP'!I14/H16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="22">
         <f>'TAHAP 3 – WP'!J14/I16</f>
         <v>0.18392019594868114</v>
       </c>
-      <c r="K11" s="49">
+      <c r="K11" s="35">
         <f>SQRT((D25-D30)^2+(E25-E30)^2+(F25-F30)^2+(G25-G30)^2+(H25-H30)^2+(I25-I30)^2+(J25-J30)^2)</f>
         <v>0.11137176995377042</v>
       </c>
-      <c r="L11" s="50">
+      <c r="L11" s="36">
         <f>SQRT((D25-D31)^2+(E25-E31)^2+(F25-F31)^2+(G25-G31)^2+(H25-H31)^2+(I25-I31)^2+(J25-J31)^2)</f>
         <v>1.0992285530562671E-2</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="29">
         <f t="shared" si="0"/>
         <v>8.9832634976454107E-2</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="7">
         <f>RANK(M11,M6:M15,0)</f>
         <v>10</v>
       </c>
-      <c r="O11" s="51" t="str">
+      <c r="O11" s="37" t="str">
         <f>'TAHAP 3 – WP'!M14</f>
         <v>K3</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20">
+      <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="str">
+      <c r="C12" s="4" t="str">
         <f>'TAHAP 3 – WP'!C15</f>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="20">
         <f>'TAHAP 3 – WP'!D15/C16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="20">
         <f>'TAHAP 3 – WP'!E15/D16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="20">
         <f>'TAHAP 3 – WP'!F15/E16</f>
         <v>0.40657855630736306</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="20">
         <f>'TAHAP 3 – WP'!G15/F16</f>
         <v>0.40575133560034449</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="20">
         <f>'TAHAP 3 – WP'!H15/G16</f>
         <v>0.35529247334746206</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="20">
         <f>'TAHAP 3 – WP'!I15/H16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="20">
         <f>'TAHAP 3 – WP'!J15/I16</f>
         <v>0.36784039189736228</v>
       </c>
-      <c r="K12" s="49">
+      <c r="K12" s="35">
         <f>SQRT((D26-D30)^2+(E26-E30)^2+(F26-F30)^2+(G26-G30)^2+(H26-H30)^2+(I26-I30)^2+(J26-J30)^2)</f>
         <v>1.1686070652631152E-2</v>
       </c>
-      <c r="L12" s="50">
+      <c r="L12" s="36">
         <f>SQRT((D26-D31)^2+(E26-E31)^2+(F26-F31)^2+(G26-G31)^2+(H26-H31)^2+(I26-I31)^2+(J26-J31)^2)</f>
         <v>0.11073421326590863</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="29">
         <f t="shared" si="0"/>
         <v>0.90454138580165988</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="7">
         <f>RANK(M12,M6:M15,0)</f>
         <v>2</v>
       </c>
-      <c r="O12" s="51" t="str">
+      <c r="O12" s="37" t="str">
         <f>'TAHAP 3 – WP'!M15</f>
         <v>K1</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="24">
+      <c r="B13" s="10">
         <v>8</v>
       </c>
-      <c r="C13" s="25" t="str">
+      <c r="C13" s="11" t="str">
         <f>'TAHAP 3 – WP'!C16</f>
         <v>Hana Putri</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="22">
         <f>'TAHAP 3 – WP'!D16/C16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="22">
         <f>'TAHAP 3 – WP'!E16/D16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="22">
         <f>'TAHAP 3 – WP'!F16/E16</f>
         <v>0.31622776601683794</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="22">
         <f>'TAHAP 3 – WP'!G16/F16</f>
         <v>0.27050089040022968</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="22">
         <f>'TAHAP 3 – WP'!H16/G16</f>
         <v>0.3108809141790293</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="22">
         <f>'TAHAP 3 – WP'!I16/H16</f>
         <v>0.27472112789737807</v>
       </c>
-      <c r="J13" s="36">
+      <c r="J13" s="22">
         <f>'TAHAP 3 – WP'!J16/I16</f>
         <v>0.321860342910192</v>
       </c>
-      <c r="K13" s="49">
+      <c r="K13" s="35">
         <f>SQRT((D27-D30)^2+(E27-E30)^2+(F27-F30)^2+(G27-G30)^2+(H27-H30)^2+(I27-I30)^2+(J27-J30)^2)</f>
         <v>6.7788219397323699E-2</v>
       </c>
-      <c r="L13" s="50">
+      <c r="L13" s="36">
         <f>SQRT((D27-D31)^2+(E27-E31)^2+(F27-F31)^2+(G27-G31)^2+(H27-H31)^2+(I27-I31)^2+(J27-J31)^2)</f>
         <v>4.9195043468407994E-2</v>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="29">
         <f t="shared" si="0"/>
         <v>0.42053061492114413</v>
       </c>
-      <c r="N13" s="21">
+      <c r="N13" s="7">
         <f>RANK(M13,M6:M15,0)</f>
         <v>6</v>
       </c>
-      <c r="O13" s="51" t="str">
+      <c r="O13" s="37" t="str">
         <f>'TAHAP 3 – WP'!M16</f>
         <v>K2</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20">
+      <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="18" t="str">
+      <c r="C14" s="4" t="str">
         <f>'TAHAP 3 – WP'!C17</f>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="20">
         <f>'TAHAP 3 – WP'!D17/C16</f>
         <v>0.36629483719650408</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="20">
         <f>'TAHAP 3 – WP'!E17/D16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="20">
         <f>'TAHAP 3 – WP'!F17/E16</f>
         <v>0.36140316116210053</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="20">
         <f>'TAHAP 3 – WP'!G17/F16</f>
         <v>0.36066785386697292</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="20">
         <f>'TAHAP 3 – WP'!H17/G16</f>
         <v>0.39970403251589481</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="20">
         <f>'TAHAP 3 – WP'!I17/H16</f>
         <v>0.41208169184606708</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="20">
         <f>'TAHAP 3 – WP'!J17/I16</f>
         <v>0.36784039189736228</v>
       </c>
-      <c r="K14" s="49">
+      <c r="K14" s="35">
         <f>SQRT((D28-D30)^2+(E28-E30)^2+(F28-F30)^2+(G28-G30)^2+(H28-H30)^2+(I28-I30)^2+(J28-J30)^2)</f>
         <v>1.9976156729128756E-2</v>
       </c>
-      <c r="L14" s="50">
+      <c r="L14" s="36">
         <f>SQRT((D28-D31)^2+(E28-E31)^2+(F28-F31)^2+(G28-G31)^2+(H28-H31)^2+(I28-I31)^2+(J28-J31)^2)</f>
         <v>9.9497350086843378E-2</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="29">
         <f t="shared" si="0"/>
         <v>0.83279843990937252</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="7">
         <f>RANK(M14,M6:M15,0)</f>
         <v>3</v>
       </c>
-      <c r="O14" s="51" t="str">
+      <c r="O14" s="37" t="str">
         <f>'TAHAP 3 – WP'!M17</f>
         <v>K1</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="24">
+      <c r="B15" s="10">
         <v>10</v>
       </c>
-      <c r="C15" s="25" t="str">
+      <c r="C15" s="11" t="str">
         <f>'TAHAP 3 – WP'!C18</f>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="22">
         <f>'TAHAP 3 – WP'!D18/C16</f>
         <v>0.22893427324781504</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="22">
         <f>'TAHAP 3 – WP'!E18/D16</f>
         <v>0.18314741859825204</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="22">
         <f>'TAHAP 3 – WP'!F18/E16</f>
         <v>0.22587697572631282</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="22">
         <f>'TAHAP 3 – WP'!G18/F16</f>
         <v>0.18033392693348646</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="22">
         <f>'TAHAP 3 – WP'!H18/G16</f>
         <v>0.22205779584216379</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="22">
         <f>'TAHAP 3 – WP'!I18/H16</f>
         <v>0.18314741859825204</v>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="22">
         <f>'TAHAP 3 – WP'!J18/I16</f>
         <v>0.22990024493585143</v>
       </c>
-      <c r="K15" s="49">
+      <c r="K15" s="35">
         <f>SQRT((D29-D30)^2+(E29-E30)^2+(F29-F30)^2+(G29-G30)^2+(H29-H30)^2+(I29-I30)^2+(J29-J30)^2)</f>
         <v>9.8599215854810532E-2</v>
       </c>
-      <c r="L15" s="50">
+      <c r="L15" s="36">
         <f>SQRT((D29-D31)^2+(E29-E31)^2+(F29-F31)^2+(G29-G31)^2+(H29-H31)^2+(I29-I31)^2+(J29-J31)^2)</f>
         <v>2.046498051176094E-2</v>
       </c>
-      <c r="M15" s="43">
+      <c r="M15" s="29">
         <f t="shared" si="0"/>
         <v>0.1718819018334776</v>
       </c>
-      <c r="N15" s="21">
+      <c r="N15" s="7">
         <f>RANK(M15,M6:M15,0)</f>
         <v>9</v>
       </c>
-      <c r="O15" s="51" t="str">
+      <c r="O15" s="37" t="str">
         <f>'TAHAP 3 – WP'!M18</f>
         <v>K3</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!D9:D18,'TAHAP 3 – WP'!D9:D18))</f>
         <v>21.840329667841555</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!E9:E18,'TAHAP 3 – WP'!E9:E18))</f>
         <v>21.840329667841555</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!F9:F18,'TAHAP 3 – WP'!F9:F18))</f>
         <v>22.135943621178654</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!G9:G18,'TAHAP 3 – WP'!G9:G18))</f>
         <v>22.181073012818835</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!H9:H18,'TAHAP 3 – WP'!H9:H18))</f>
         <v>22.516660498395403</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!I9:I18,'TAHAP 3 – WP'!I9:I18))</f>
         <v>21.840329667841555</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="30">
         <f>SQRT(SUMPRODUCT('TAHAP 3 – WP'!J9:J18,'TAHAP 3 – WP'!J9:J18))</f>
         <v>21.748563170931547</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
     </row>
     <row r="19" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="20">
+      <c r="B20" s="6">
         <v>1</v>
       </c>
-      <c r="C20" s="18" t="str">
+      <c r="C20" s="4" t="str">
         <f t="shared" ref="C20:C29" si="1">C6</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="20">
         <f>D6*'TAHAP 3 – WP'!C6</f>
         <v>0.15315384825478631</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="20">
         <f>E6*'TAHAP 3 – WP'!D6</f>
         <v>7.3465498927491615E-2</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="20">
         <f>F6*'TAHAP 3 – WP'!E6</f>
         <v>4.5799406820628233E-2</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="20">
         <f>G6*'TAHAP 3 – WP'!F6</f>
         <v>1.8346387893753882E-2</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="20">
         <f>H6*'TAHAP 3 – WP'!G6</f>
         <v>4.502501991079446E-2</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="20">
         <f>I6*'TAHAP 3 – WP'!H6</f>
         <v>1.6303542741071386E-2</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="20">
         <f>J6*'TAHAP 3 – WP'!I6</f>
         <v>9.4315847042009075E-3</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24">
+      <c r="B21" s="10">
         <v>2</v>
       </c>
-      <c r="C21" s="25" t="str">
+      <c r="C21" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Budi Santoso</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="22">
         <f>D7*'TAHAP 3 – WP'!C6</f>
         <v>9.5721155159241442E-2</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="22">
         <f>E7*'TAHAP 3 – WP'!D6</f>
         <v>6.2970427652135674E-2</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="22">
         <f>F7*'TAHAP 3 – WP'!E6</f>
         <v>2.5444114900349021E-2</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="22">
         <f>G7*'TAHAP 3 – WP'!F6</f>
         <v>1.375979092031541E-2</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="22">
         <f>H7*'TAHAP 3 – WP'!G6</f>
         <v>2.5013899950441364E-2</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="22">
         <f>I7*'TAHAP 3 – WP'!H6</f>
         <v>1.3974465206632617E-2</v>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="22">
         <f>J7*'TAHAP 3 – WP'!I6</f>
         <v>5.8947404401255669E-3</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="20">
+      <c r="B22" s="6">
         <v>3</v>
       </c>
-      <c r="C22" s="18" t="str">
+      <c r="C22" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Citra Dewi</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="20">
         <f>D8*'TAHAP 3 – WP'!C6</f>
         <v>0.1722980792866346</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="20">
         <f>E8*'TAHAP 3 – WP'!D6</f>
         <v>9.4455641478203498E-2</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="20">
         <f>F8*'TAHAP 3 – WP'!E6</f>
         <v>4.0710583840558437E-2</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="20">
         <f>G8*'TAHAP 3 – WP'!F6</f>
         <v>2.0639686380473116E-2</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="20">
         <f>H8*'TAHAP 3 – WP'!G6</f>
         <v>4.502501991079446E-2</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="20">
         <f>I8*'TAHAP 3 – WP'!H6</f>
         <v>1.8632620275510155E-2</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="20">
         <f>J8*'TAHAP 3 – WP'!I6</f>
         <v>1.0610532792226022E-2</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="24">
+      <c r="B23" s="10">
         <v>4</v>
       </c>
-      <c r="C23" s="25" t="str">
+      <c r="C23" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="22">
         <f>D9*'TAHAP 3 – WP'!C6</f>
         <v>0.11486538619108973</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="22">
         <f>E9*'TAHAP 3 – WP'!D6</f>
         <v>5.2475356376779719E-2</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="22">
         <f>F9*'TAHAP 3 – WP'!E6</f>
         <v>3.0532937880418828E-2</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="22">
         <f>G9*'TAHAP 3 – WP'!F6</f>
         <v>1.1466492433596175E-2</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="22">
         <f>H9*'TAHAP 3 – WP'!G6</f>
         <v>3.0016679940529638E-2</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="22">
         <f>I9*'TAHAP 3 – WP'!H6</f>
         <v>1.1645387672193846E-2</v>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="22">
         <f>J9*'TAHAP 3 – WP'!I6</f>
         <v>7.073688528150681E-3</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="20">
+      <c r="B24" s="6">
         <v>5</v>
       </c>
-      <c r="C24" s="18" t="str">
+      <c r="C24" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="20">
         <f>D10*'TAHAP 3 – WP'!C6</f>
         <v>0.13400961722293803</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="20">
         <f>E10*'TAHAP 3 – WP'!D6</f>
         <v>8.3960570202847556E-2</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="20">
         <f>F10*'TAHAP 3 – WP'!E6</f>
         <v>3.5621760860488627E-2</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="20">
         <f>G10*'TAHAP 3 – WP'!F6</f>
         <v>1.8346387893753882E-2</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="20">
         <f>H10*'TAHAP 3 – WP'!G6</f>
         <v>3.5019459930617912E-2</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="20">
         <f>I10*'TAHAP 3 – WP'!H6</f>
         <v>1.8632620275510155E-2</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="20">
         <f>J10*'TAHAP 3 – WP'!I6</f>
         <v>8.2526366161757951E-3</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="24">
+      <c r="B25" s="10">
         <v>6</v>
       </c>
-      <c r="C25" s="25" t="str">
+      <c r="C25" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="22">
         <f>D11*'TAHAP 3 – WP'!C6</f>
         <v>7.6576924127393156E-2</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="22">
         <f>E11*'TAHAP 3 – WP'!D6</f>
         <v>5.2475356376779719E-2</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="22">
         <f>F11*'TAHAP 3 – WP'!E6</f>
         <v>2.0355291920279218E-2</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="22">
         <f>G11*'TAHAP 3 – WP'!F6</f>
         <v>1.1466492433596175E-2</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="22">
         <f>H11*'TAHAP 3 – WP'!G6</f>
         <v>2.0011119960353093E-2</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="22">
         <f>I11*'TAHAP 3 – WP'!H6</f>
         <v>1.1645387672193846E-2</v>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="22">
         <f>J11*'TAHAP 3 – WP'!I6</f>
         <v>4.7157923521004537E-3</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="20">
+      <c r="B26" s="6">
         <v>7</v>
       </c>
-      <c r="C26" s="18" t="str">
+      <c r="C26" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="20">
         <f>D12*'TAHAP 3 – WP'!C6</f>
         <v>0.1722980792866346</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="20">
         <f>E12*'TAHAP 3 – WP'!D6</f>
         <v>8.3960570202847556E-2</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="20">
         <f>F12*'TAHAP 3 – WP'!E6</f>
         <v>4.5799406820628233E-2</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="20">
         <f>G12*'TAHAP 3 – WP'!F6</f>
         <v>2.0639686380473116E-2</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="20">
         <f>H12*'TAHAP 3 – WP'!G6</f>
         <v>4.0022239920706186E-2</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="20">
         <f>I12*'TAHAP 3 – WP'!H6</f>
         <v>2.0961697809948925E-2</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="20">
         <f>J12*'TAHAP 3 – WP'!I6</f>
         <v>9.4315847042009075E-3</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="24">
+      <c r="B27" s="10">
         <v>8</v>
       </c>
-      <c r="C27" s="25" t="str">
+      <c r="C27" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Hana Putri</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="22">
         <f>D13*'TAHAP 3 – WP'!C6</f>
         <v>0.11486538619108973</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="22">
         <f>E13*'TAHAP 3 – WP'!D6</f>
         <v>6.2970427652135674E-2</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="22">
         <f>F13*'TAHAP 3 – WP'!E6</f>
         <v>3.5621760860488627E-2</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="22">
         <f>G13*'TAHAP 3 – WP'!F6</f>
         <v>1.375979092031541E-2</v>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="22">
         <f>H13*'TAHAP 3 – WP'!G6</f>
         <v>3.5019459930617912E-2</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="22">
         <f>I13*'TAHAP 3 – WP'!H6</f>
         <v>1.3974465206632617E-2</v>
       </c>
-      <c r="J27" s="36">
+      <c r="J27" s="22">
         <f>J13*'TAHAP 3 – WP'!I6</f>
         <v>8.2526366161757951E-3</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="20">
+      <c r="B28" s="6">
         <v>9</v>
       </c>
-      <c r="C28" s="18" t="str">
+      <c r="C28" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="20">
         <f>D14*'TAHAP 3 – WP'!C6</f>
         <v>0.15315384825478631</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="20">
         <f>E14*'TAHAP 3 – WP'!D6</f>
         <v>9.4455641478203498E-2</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="20">
         <f>F14*'TAHAP 3 – WP'!E6</f>
         <v>4.0710583840558437E-2</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="20">
         <f>G14*'TAHAP 3 – WP'!F6</f>
         <v>1.8346387893753882E-2</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="20">
         <f>H14*'TAHAP 3 – WP'!G6</f>
         <v>4.502501991079446E-2</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="20">
         <f>I14*'TAHAP 3 – WP'!H6</f>
         <v>2.0961697809948925E-2</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="20">
         <f>J14*'TAHAP 3 – WP'!I6</f>
         <v>9.4315847042009075E-3</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="24">
+      <c r="B29" s="10">
         <v>10</v>
       </c>
-      <c r="C29" s="25" t="str">
+      <c r="C29" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="22">
         <f>D15*'TAHAP 3 – WP'!C6</f>
         <v>9.5721155159241442E-2</v>
       </c>
-      <c r="E29" s="36">
+      <c r="E29" s="22">
         <f>E15*'TAHAP 3 – WP'!D6</f>
         <v>4.1980285101423778E-2</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="22">
         <f>F15*'TAHAP 3 – WP'!E6</f>
         <v>2.5444114900349021E-2</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="22">
         <f>G15*'TAHAP 3 – WP'!F6</f>
         <v>9.1731939468769411E-3</v>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="22">
         <f>H15*'TAHAP 3 – WP'!G6</f>
         <v>2.5013899950441364E-2</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="22">
         <f>I15*'TAHAP 3 – WP'!H6</f>
         <v>9.3163101377550777E-3</v>
       </c>
-      <c r="J29" s="36">
+      <c r="J29" s="22">
         <f>J15*'TAHAP 3 – WP'!I6</f>
         <v>5.8947404401255669E-3</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="50">
+      <c r="D30" s="36">
         <f t="shared" ref="D30:J30" si="2">MAX(D20:D29)</f>
         <v>0.1722980792866346</v>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="36">
         <f t="shared" si="2"/>
         <v>9.4455641478203498E-2</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="36">
         <f t="shared" si="2"/>
         <v>4.5799406820628233E-2</v>
       </c>
-      <c r="G30" s="50">
+      <c r="G30" s="36">
         <f t="shared" si="2"/>
         <v>2.0639686380473116E-2</v>
       </c>
-      <c r="H30" s="50">
+      <c r="H30" s="36">
         <f t="shared" si="2"/>
         <v>4.502501991079446E-2</v>
       </c>
-      <c r="I30" s="50">
+      <c r="I30" s="36">
         <f t="shared" si="2"/>
         <v>2.0961697809948925E-2</v>
       </c>
-      <c r="J30" s="50">
+      <c r="J30" s="36">
         <f t="shared" si="2"/>
         <v>1.0610532792226022E-2</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="35">
         <f t="shared" ref="D31:J31" si="3">MIN(D20:D29)</f>
         <v>7.6576924127393156E-2</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="35">
         <f t="shared" si="3"/>
         <v>4.1980285101423778E-2</v>
       </c>
-      <c r="F31" s="49">
+      <c r="F31" s="35">
         <f t="shared" si="3"/>
         <v>2.0355291920279218E-2</v>
       </c>
-      <c r="G31" s="49">
+      <c r="G31" s="35">
         <f t="shared" si="3"/>
         <v>9.1731939468769411E-3</v>
       </c>
-      <c r="H31" s="49">
+      <c r="H31" s="35">
         <f t="shared" si="3"/>
         <v>2.0011119960353093E-2</v>
       </c>
-      <c r="I31" s="49">
+      <c r="I31" s="35">
         <f t="shared" si="3"/>
         <v>9.3163101377550777E-3</v>
       </c>
-      <c r="J31" s="49">
+      <c r="J31" s="35">
         <f t="shared" si="3"/>
         <v>4.7157923521004537E-3</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="60"/>
+      <c r="L33" s="60"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="60"/>
     </row>
     <row r="34" spans="2:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="20">
+      <c r="B35" s="6">
         <v>1</v>
       </c>
-      <c r="C35" s="18" t="str">
+      <c r="C35" s="4" t="str">
         <f>'TAHAP 3 – WP'!C9</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="33">
         <f>'TAHAP 3 – WP'!L9</f>
         <v>4</v>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="33">
         <f t="shared" ref="E35:E44" si="4">N6</f>
         <v>4</v>
       </c>
-      <c r="F35" s="47">
+      <c r="F35" s="33">
         <f t="shared" ref="F35:F44" si="5">ABS(D35-E35)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="23" t="str">
+      <c r="G35" s="9" t="str">
         <f t="shared" ref="G35:G44" si="6">IF(F35&lt;=1,"✔ YA","✘ TIDAK")</f>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="24">
+      <c r="B36" s="10">
         <v>2</v>
       </c>
-      <c r="C36" s="25" t="str">
+      <c r="C36" s="11" t="str">
         <f>'TAHAP 3 – WP'!C10</f>
         <v>Budi Santoso</v>
       </c>
-      <c r="D36" s="48">
+      <c r="D36" s="34">
         <f>'TAHAP 3 – WP'!L10</f>
         <v>8</v>
       </c>
-      <c r="E36" s="48">
+      <c r="E36" s="34">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G36" s="23" t="str">
+      <c r="G36" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="37" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="20">
+      <c r="B37" s="6">
         <v>3</v>
       </c>
-      <c r="C37" s="18" t="str">
+      <c r="C37" s="4" t="str">
         <f>'TAHAP 3 – WP'!C11</f>
         <v>Citra Dewi</v>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="33">
         <f>'TAHAP 3 – WP'!L11</f>
         <v>1</v>
       </c>
-      <c r="E37" s="47">
+      <c r="E37" s="33">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F37" s="47">
+      <c r="F37" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G37" s="23" t="str">
+      <c r="G37" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="38" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="24">
+      <c r="B38" s="10">
         <v>4</v>
       </c>
-      <c r="C38" s="25" t="str">
+      <c r="C38" s="11" t="str">
         <f>'TAHAP 3 – WP'!C12</f>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D38" s="48">
+      <c r="D38" s="34">
         <f>'TAHAP 3 – WP'!L12</f>
         <v>7</v>
       </c>
-      <c r="E38" s="48">
+      <c r="E38" s="34">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F38" s="48">
+      <c r="F38" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G38" s="23" t="str">
+      <c r="G38" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="39" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="20">
+      <c r="B39" s="6">
         <v>5</v>
       </c>
-      <c r="C39" s="18" t="str">
+      <c r="C39" s="4" t="str">
         <f>'TAHAP 3 – WP'!C13</f>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D39" s="47">
+      <c r="D39" s="33">
         <f>'TAHAP 3 – WP'!L13</f>
         <v>5</v>
       </c>
-      <c r="E39" s="47">
+      <c r="E39" s="33">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F39" s="47">
+      <c r="F39" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G39" s="23" t="str">
+      <c r="G39" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="24">
+      <c r="B40" s="10">
         <v>6</v>
       </c>
-      <c r="C40" s="25" t="str">
+      <c r="C40" s="11" t="str">
         <f>'TAHAP 3 – WP'!C14</f>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D40" s="48">
+      <c r="D40" s="34">
         <f>'TAHAP 3 – WP'!L14</f>
         <v>10</v>
       </c>
-      <c r="E40" s="48">
+      <c r="E40" s="34">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G40" s="23" t="str">
+      <c r="G40" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="20">
+      <c r="B41" s="6">
         <v>7</v>
       </c>
-      <c r="C41" s="18" t="str">
+      <c r="C41" s="4" t="str">
         <f>'TAHAP 3 – WP'!C15</f>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D41" s="33">
         <f>'TAHAP 3 – WP'!L15</f>
         <v>2</v>
       </c>
-      <c r="E41" s="47">
+      <c r="E41" s="33">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F41" s="47">
+      <c r="F41" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G41" s="23" t="str">
+      <c r="G41" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="42" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="24">
+      <c r="B42" s="10">
         <v>8</v>
       </c>
-      <c r="C42" s="25" t="str">
+      <c r="C42" s="11" t="str">
         <f>'TAHAP 3 – WP'!C16</f>
         <v>Hana Putri</v>
       </c>
-      <c r="D42" s="48">
+      <c r="D42" s="34">
         <f>'TAHAP 3 – WP'!L16</f>
         <v>6</v>
       </c>
-      <c r="E42" s="48">
+      <c r="E42" s="34">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F42" s="48">
+      <c r="F42" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G42" s="23" t="str">
+      <c r="G42" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="43" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="20">
+      <c r="B43" s="6">
         <v>9</v>
       </c>
-      <c r="C43" s="18" t="str">
+      <c r="C43" s="4" t="str">
         <f>'TAHAP 3 – WP'!C17</f>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D43" s="47">
+      <c r="D43" s="33">
         <f>'TAHAP 3 – WP'!L17</f>
         <v>3</v>
       </c>
-      <c r="E43" s="47">
+      <c r="E43" s="33">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F43" s="47">
+      <c r="F43" s="33">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G43" s="23" t="str">
+      <c r="G43" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="44" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="24">
+      <c r="B44" s="10">
         <v>10</v>
       </c>
-      <c r="C44" s="25" t="str">
+      <c r="C44" s="11" t="str">
         <f>'TAHAP 3 – WP'!C18</f>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D44" s="48">
+      <c r="D44" s="34">
         <f>'TAHAP 3 – WP'!L18</f>
         <v>9</v>
       </c>
-      <c r="E44" s="48">
+      <c r="E44" s="34">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F44" s="48">
+      <c r="F44" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G44" s="23" t="str">
+      <c r="G44" s="9" t="str">
         <f t="shared" si="6"/>
         <v>✔ YA</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="64"/>
+      <c r="L46" s="64"/>
+      <c r="M46" s="64"/>
+      <c r="N46" s="64"/>
     </row>
     <row r="47" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H47" s="55">
+      <c r="H47" s="41">
         <f>COUNTIF(G35:G44,"✔ YA")/10</f>
         <v>1</v>
       </c>
@@ -5671,584 +5671,586 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="22" style="15" customWidth="1"/>
-    <col min="3" max="6" width="13" style="15" customWidth="1"/>
-    <col min="7" max="7" width="12" style="15" customWidth="1"/>
-    <col min="8" max="8" width="18" style="15" customWidth="1"/>
-    <col min="9" max="9" width="20" style="15" customWidth="1"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
+    <col min="4" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
     </row>
     <row r="4" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
     </row>
     <row r="5" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="20">
+    <row r="6" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="str">
+      <c r="C6" s="4" t="str">
         <f>'TAHAP 3 – WP'!C9</f>
         <v>Andi Setiawan</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="20">
         <f>'TAHAP 3 – WP'!K9</f>
         <v>7.9135551847656185</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="33">
         <f>'TAHAP 3 – WP'!L9</f>
         <v>4</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="20">
         <f>'TAHAP 4 – TOPSIS'!M6</f>
         <v>0.75897040763437995</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="33">
         <f>'TAHAP 4 – TOPSIS'!N6</f>
         <v>4</v>
       </c>
-      <c r="H6" s="35" t="str">
+      <c r="H6" s="21" t="str">
         <f>'TAHAP 3 – WP'!M9</f>
         <v>K1</v>
       </c>
-      <c r="I6" s="71">
+      <c r="I6" s="54">
         <f t="shared" ref="I6:I15" si="0">(D6+F6)/2</f>
         <v>4.3362627961999989</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="42">
         <f>RANK(I6,I6:I15,0)</f>
         <v>4</v>
       </c>
-      <c r="K6" s="57" t="str">
+      <c r="K6" s="43" t="str">
         <f t="shared" ref="K6:K15" si="1">IF(H6="K1","Promosi / Pengembangan Lanjut",IF(H6="K2","Pertahankan &amp; Tingkatkan","Perlu Pembinaan Intensif"))</f>
         <v>Promosi / Pengembangan Lanjut</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="10">
         <v>2</v>
       </c>
-      <c r="C7" s="25" t="str">
+      <c r="C7" s="11" t="str">
         <f>'TAHAP 3 – WP'!C10</f>
         <v>Budi Santoso</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="22">
         <f>'TAHAP 3 – WP'!K10</f>
         <v>5.3109859588063157</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="34">
         <f>'TAHAP 3 – WP'!L10</f>
         <v>8</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="22">
         <f>'TAHAP 4 – TOPSIS'!M7</f>
         <v>0.25391878693683295</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="34">
         <f>'TAHAP 4 – TOPSIS'!N7</f>
         <v>8</v>
       </c>
-      <c r="H7" s="37" t="str">
+      <c r="H7" s="23" t="str">
         <f>'TAHAP 3 – WP'!M10</f>
         <v>K3</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="54">
         <f t="shared" si="0"/>
         <v>2.7824523728715742</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="42">
         <f>RANK(I7,I6:I15,0)</f>
         <v>8</v>
       </c>
-      <c r="K7" s="58" t="str">
+      <c r="K7" s="44" t="str">
         <f t="shared" si="1"/>
         <v>Perlu Pembinaan Intensif</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="20">
+    <row r="8" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="18" t="str">
+      <c r="C8" s="4" t="str">
         <f>'TAHAP 3 – WP'!C11</f>
         <v>Citra Dewi</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="20">
         <f>'TAHAP 3 – WP'!K11</f>
         <v>8.8283261711137531</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="33">
         <f>'TAHAP 3 – WP'!L11</f>
         <v>1</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="20">
         <f>'TAHAP 4 – TOPSIS'!M8</f>
         <v>0.95356688366418274</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="33">
         <f>'TAHAP 4 – TOPSIS'!N8</f>
         <v>1</v>
       </c>
-      <c r="H8" s="35" t="str">
+      <c r="H8" s="21" t="str">
         <f>'TAHAP 3 – WP'!M11</f>
         <v>K1</v>
       </c>
-      <c r="I8" s="71">
+      <c r="I8" s="54">
         <f t="shared" si="0"/>
         <v>4.8909465273889676</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="42">
         <f>RANK(I8,I6:I15,0)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="57" t="str">
+      <c r="K8" s="43" t="str">
         <f t="shared" si="1"/>
         <v>Promosi / Pengembangan Lanjut</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="10">
         <v>4</v>
       </c>
-      <c r="C9" s="25" t="str">
+      <c r="C9" s="11" t="str">
         <f>'TAHAP 3 – WP'!C12</f>
         <v>Dian Pratiwi</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="22">
         <f>'TAHAP 3 – WP'!K12</f>
         <v>5.6486686714462202</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="34">
         <f>'TAHAP 3 – WP'!L12</f>
         <v>7</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="22">
         <f>'TAHAP 4 – TOPSIS'!M9</f>
         <v>0.35947198209646375</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="34">
         <f>'TAHAP 4 – TOPSIS'!N9</f>
         <v>7</v>
       </c>
-      <c r="H9" s="37" t="str">
+      <c r="H9" s="23" t="str">
         <f>'TAHAP 3 – WP'!M12</f>
         <v>K2</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="54">
         <f t="shared" si="0"/>
         <v>3.004070326771342</v>
       </c>
-      <c r="J9" s="56">
+      <c r="J9" s="42">
         <f>RANK(I9,I6:I15,0)</f>
         <v>7</v>
       </c>
-      <c r="K9" s="58" t="str">
+      <c r="K9" s="44" t="str">
         <f t="shared" si="1"/>
         <v>Pertahankan &amp; Tingkatkan</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="20">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="18" t="str">
+      <c r="C10" s="4" t="str">
         <f>'TAHAP 3 – WP'!C13</f>
         <v>Eko Wahyudi</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="20">
         <f>'TAHAP 3 – WP'!K13</f>
         <v>7.3162840691386792</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="33">
         <f>'TAHAP 3 – WP'!L13</f>
         <v>5</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="20">
         <f>'TAHAP 4 – TOPSIS'!M10</f>
         <v>0.6405280179035362</v>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="33">
         <f>'TAHAP 4 – TOPSIS'!N10</f>
         <v>5</v>
       </c>
-      <c r="H10" s="35" t="str">
+      <c r="H10" s="21" t="str">
         <f>'TAHAP 3 – WP'!M13</f>
         <v>K2</v>
       </c>
-      <c r="I10" s="71">
+      <c r="I10" s="54">
         <f t="shared" si="0"/>
         <v>3.9784060435211077</v>
       </c>
-      <c r="J10" s="56">
+      <c r="J10" s="42">
         <f>RANK(I10,I6:I15,0)</f>
         <v>5</v>
       </c>
-      <c r="K10" s="57" t="str">
+      <c r="K10" s="43" t="str">
         <f t="shared" si="1"/>
         <v>Pertahankan &amp; Tingkatkan</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="10">
         <v>6</v>
       </c>
-      <c r="C11" s="25" t="str">
+      <c r="C11" s="11" t="str">
         <f>'TAHAP 3 – WP'!C14</f>
         <v>Fitri Handayani</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="22">
         <f>'TAHAP 3 – WP'!K14</f>
         <v>4.3065798248266693</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="34">
         <f>'TAHAP 3 – WP'!L14</f>
         <v>10</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="22">
         <f>'TAHAP 4 – TOPSIS'!M11</f>
         <v>8.9832634976454107E-2</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="34">
         <f>'TAHAP 4 – TOPSIS'!N11</f>
         <v>10</v>
       </c>
-      <c r="H11" s="37" t="str">
+      <c r="H11" s="23" t="str">
         <f>'TAHAP 3 – WP'!M14</f>
         <v>K3</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="54">
         <f t="shared" si="0"/>
         <v>2.1982062299015617</v>
       </c>
-      <c r="J11" s="56">
+      <c r="J11" s="42">
         <f>RANK(I11,I6:I15,0)</f>
         <v>10</v>
       </c>
-      <c r="K11" s="58" t="str">
+      <c r="K11" s="44" t="str">
         <f t="shared" si="1"/>
         <v>Perlu Pembinaan Intensif</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="20">
+    <row r="12" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="str">
+      <c r="C12" s="4" t="str">
         <f>'TAHAP 3 – WP'!C15</f>
         <v>Galih Nugroho</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="20">
         <f>'TAHAP 3 – WP'!K15</f>
         <v>8.6187413542836833</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="33">
         <f>'TAHAP 3 – WP'!L15</f>
         <v>2</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="20">
         <f>'TAHAP 4 – TOPSIS'!M12</f>
         <v>0.90454138580165988</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="33">
         <f>'TAHAP 4 – TOPSIS'!N12</f>
         <v>2</v>
       </c>
-      <c r="H12" s="35" t="str">
+      <c r="H12" s="21" t="str">
         <f>'TAHAP 3 – WP'!M15</f>
         <v>K1</v>
       </c>
-      <c r="I12" s="71">
+      <c r="I12" s="54">
         <f t="shared" si="0"/>
         <v>4.7616413700426712</v>
       </c>
-      <c r="J12" s="56">
+      <c r="J12" s="42">
         <f>RANK(I12,I6:I15,0)</f>
         <v>2</v>
       </c>
-      <c r="K12" s="57" t="str">
+      <c r="K12" s="43" t="str">
         <f t="shared" si="1"/>
         <v>Promosi / Pengembangan Lanjut</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="24">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="10">
         <v>8</v>
       </c>
-      <c r="C13" s="25" t="str">
+      <c r="C13" s="11" t="str">
         <f>'TAHAP 3 – WP'!C16</f>
         <v>Hana Putri</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="22">
         <f>'TAHAP 3 – WP'!K16</f>
         <v>6.2366354244847422</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="34">
         <f>'TAHAP 3 – WP'!L16</f>
         <v>6</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="22">
         <f>'TAHAP 4 – TOPSIS'!M13</f>
         <v>0.42053061492114413</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="34">
         <f>'TAHAP 4 – TOPSIS'!N13</f>
         <v>6</v>
       </c>
-      <c r="H13" s="37" t="str">
+      <c r="H13" s="23" t="str">
         <f>'TAHAP 3 – WP'!M16</f>
         <v>K2</v>
       </c>
-      <c r="I13" s="71">
+      <c r="I13" s="54">
         <f t="shared" si="0"/>
         <v>3.3285830197029433</v>
       </c>
-      <c r="J13" s="56">
+      <c r="J13" s="42">
         <f>RANK(I13,I6:I15,0)</f>
         <v>6</v>
       </c>
-      <c r="K13" s="58" t="str">
+      <c r="K13" s="44" t="str">
         <f t="shared" si="1"/>
         <v>Pertahankan &amp; Tingkatkan</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20">
+    <row r="14" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="18" t="str">
+      <c r="C14" s="4" t="str">
         <f>'TAHAP 3 – WP'!C17</f>
         <v>Indra Kusuma</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="20">
         <f>'TAHAP 3 – WP'!K17</f>
         <v>8.3787473185254893</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="33">
         <f>'TAHAP 3 – WP'!L17</f>
         <v>3</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="20">
         <f>'TAHAP 4 – TOPSIS'!M14</f>
         <v>0.83279843990937252</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="33">
         <f>'TAHAP 4 – TOPSIS'!N14</f>
         <v>3</v>
       </c>
-      <c r="H14" s="35" t="str">
+      <c r="H14" s="21" t="str">
         <f>'TAHAP 3 – WP'!M17</f>
         <v>K1</v>
       </c>
-      <c r="I14" s="71">
+      <c r="I14" s="54">
         <f t="shared" si="0"/>
         <v>4.6057728792174313</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="42">
         <f>RANK(I14,I6:I15,0)</f>
         <v>3</v>
       </c>
-      <c r="K14" s="57" t="str">
+      <c r="K14" s="43" t="str">
         <f t="shared" si="1"/>
         <v>Promosi / Pengembangan Lanjut</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="24">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="10">
         <v>10</v>
       </c>
-      <c r="C15" s="25" t="str">
+      <c r="C15" s="11" t="str">
         <f>'TAHAP 3 – WP'!C18</f>
         <v>Joko Purnomo</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="22">
         <f>'TAHAP 3 – WP'!K18</f>
         <v>4.6440564934390753</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="34">
         <f>'TAHAP 3 – WP'!L18</f>
         <v>9</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="22">
         <f>'TAHAP 4 – TOPSIS'!M15</f>
         <v>0.1718819018334776</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="34">
         <f>'TAHAP 4 – TOPSIS'!N15</f>
         <v>9</v>
       </c>
-      <c r="H15" s="37" t="str">
+      <c r="H15" s="23" t="str">
         <f>'TAHAP 3 – WP'!M18</f>
         <v>K3</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="54">
         <f t="shared" si="0"/>
         <v>2.4079691976362763</v>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="42">
         <f>RANK(I15,I6:I15,0)</f>
         <v>9</v>
       </c>
-      <c r="K15" s="58" t="str">
+      <c r="K15" s="44" t="str">
         <f t="shared" si="1"/>
         <v>Perlu Pembinaan Intensif</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
     </row>
     <row r="18" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
     </row>
     <row r="19" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="45">
         <f>COUNTIF(H6:H15,"K1")</f>
         <v>4</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="28">
         <f>AVERAGEIF(H6:H15,"K1",D6:D15)</f>
         <v>8.4348425071721369</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="28">
         <f>AVERAGEIF(H6:H15,"K1",F6:F15)</f>
         <v>0.8624692792523988</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="60" t="s">
+      <c r="B20" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="61">
+      <c r="C20" s="47">
         <f>COUNTIF(H6:H15,"K2")</f>
         <v>3</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D20" s="48">
         <f>AVERAGEIF(H6:H15,"K2",D6:D15)</f>
         <v>6.4005293883565466</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E20" s="48">
         <f>AVERAGEIF(H6:H15,"K2",F6:F15)</f>
         <v>0.47351020497371471</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="49">
         <f>COUNTIF(H6:H15,"K3")</f>
         <v>3</v>
       </c>
-      <c r="D21" s="64">
+      <c r="D21" s="50">
         <f>AVERAGEIF(H6:H15,"K3",D6:D15)</f>
         <v>4.7538740923573535</v>
       </c>
-      <c r="E21" s="64">
+      <c r="E21" s="50">
         <f>AVERAGEIF(H6:H15,"K3",F6:F15)</f>
         <v>0.17187777458225487</v>
       </c>
@@ -6260,19 +6262,19 @@
       <c r="I21" s="68"/>
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
     </row>
     <row r="24" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="25" t="s">
         <v>147</v>
       </c>
       <c r="C24" s="69" t="s">
@@ -6286,107 +6288,107 @@
       <c r="I24" s="69"/>
     </row>
     <row r="25" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="65" t="s">
+      <c r="B25" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
     </row>
     <row r="26" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="65" t="s">
+      <c r="B26" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
     </row>
     <row r="27" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
     </row>
     <row r="28" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="65" t="s">
+      <c r="B28" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
     </row>
     <row r="29" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
     </row>
     <row r="30" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="53" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="C27:I27"/>
     <mergeCell ref="C28:I28"/>
     <mergeCell ref="C29:I29"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="F18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
